--- a/Plannings 2026 S16.xlsx
+++ b/Plannings 2026 S16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3A5B07A-8FED-4E31-BA69-31D742EA78EE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="145">
   <si>
     <t>Planning des salariés du 13/04/2026 au 19/04/2026</t>
   </si>
@@ -451,6 +451,12 @@
   </si>
   <si>
     <t>LOUIBA Yacine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. PADEL // </t>
+  </si>
+  <si>
+    <t>P50M // ANIV</t>
   </si>
 </sst>
 </file>
@@ -846,7 +852,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -956,9 +962,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -981,9 +984,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1026,6 +1026,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5675,13 +5684,17 @@
       <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="15"/>
+      <c r="B3" s="15" t="s">
+        <v>143</v>
+      </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
+      <c r="H3" s="15" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
@@ -5801,16 +5814,16 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="24"/>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="1"/>
@@ -5819,16 +5832,16 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="24"/>
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="41" t="s">
         <v>27</v>
       </c>
       <c r="F12" s="1"/>
@@ -5840,13 +5853,13 @@
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="42"/>
+      <c r="E13" s="41"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="25"/>
@@ -5856,13 +5869,13 @@
       <c r="B14" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="43" t="s">
+      <c r="D14" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="43"/>
+      <c r="E14" s="42"/>
       <c r="F14" s="22"/>
       <c r="G14" s="22"/>
       <c r="H14" s="23"/>
@@ -5879,7 +5892,7 @@
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
-      <c r="H15" s="36" t="s">
+      <c r="H15" s="44" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5893,7 +5906,7 @@
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
-      <c r="H16" s="37" t="s">
+      <c r="H16" s="61" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5964,7 +5977,7 @@
       <c r="F20" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="60" t="s">
+      <c r="G20" s="58" t="s">
         <v>43</v>
       </c>
       <c r="H20" s="19"/>
@@ -5980,7 +5993,7 @@
       <c r="F21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G21" s="59" t="s">
+      <c r="G21" s="57" t="s">
         <v>46</v>
       </c>
       <c r="H21" s="25"/>
@@ -6013,41 +6026,41 @@
       <c r="A24" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="52" t="s">
+      <c r="C24" s="50" t="s">
         <v>49</v>
       </c>
       <c r="D24" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="41" t="s">
+      <c r="E24" s="40" t="s">
         <v>23</v>
       </c>
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
-      <c r="H24" s="45" t="s">
+      <c r="H24" s="59" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="24"/>
-      <c r="B25" s="53" t="s">
+      <c r="B25" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="53" t="s">
+      <c r="C25" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="D25" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="E25" s="42" t="s">
+      <c r="E25" s="41" t="s">
         <v>27</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="46" t="s">
+      <c r="H25" s="60" t="s">
         <v>53</v>
       </c>
     </row>
@@ -6059,10 +6072,10 @@
       <c r="C26" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="39" t="s">
+      <c r="D26" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="42"/>
+      <c r="E26" s="41"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="31" t="s">
@@ -6077,10 +6090,10 @@
       <c r="C27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="38" t="s">
+      <c r="D27" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="42"/>
+      <c r="E27" s="41"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="25" t="s">
@@ -6089,76 +6102,76 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C28" s="49" t="s">
         <v>49</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="42"/>
+      <c r="E28" s="41"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="25"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="53" t="s">
+      <c r="C29" s="51" t="s">
         <v>61</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="42"/>
+      <c r="E29" s="41"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="25"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="24"/>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="38" t="s">
         <v>49</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="51" t="s">
+      <c r="D30" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="E30" s="42"/>
+      <c r="E30" s="41"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="25"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="24"/>
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="37" t="s">
         <v>63</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="53" t="s">
+      <c r="D31" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="E31" s="42"/>
+      <c r="E31" s="41"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="25"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="24"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="51" t="s">
+      <c r="B32" s="37"/>
+      <c r="C32" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="42"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="41"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="25"/>
@@ -6170,7 +6183,7 @@
         <v>66</v>
       </c>
       <c r="D33" s="35"/>
-      <c r="E33" s="43"/>
+      <c r="E33" s="42"/>
       <c r="F33" s="22"/>
       <c r="G33" s="22"/>
       <c r="H33" s="23"/>
@@ -6225,7 +6238,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="24"/>
-      <c r="B37" s="38" t="s">
+      <c r="B37" s="37" t="s">
         <v>20</v>
       </c>
       <c r="C37" s="1"/>
@@ -6235,21 +6248,21 @@
       <c r="E37" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F37" s="38" t="s">
+      <c r="F37" s="37" t="s">
         <v>20</v>
       </c>
       <c r="G37" s="1"/>
-      <c r="H37" s="40" t="s">
+      <c r="H37" s="39" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="24"/>
-      <c r="B38" s="44" t="s">
+      <c r="B38" s="43" t="s">
         <v>73</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="39" t="s">
+      <c r="D38" s="38" t="s">
         <v>74</v>
       </c>
       <c r="E38" s="1"/>
@@ -6257,17 +6270,17 @@
         <v>15</v>
       </c>
       <c r="G38" s="1"/>
-      <c r="H38" s="56" t="s">
+      <c r="H38" s="54" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="24"/>
-      <c r="B39" s="42" t="s">
+      <c r="B39" s="41" t="s">
         <v>76</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="38" t="s">
+      <c r="D39" s="37" t="s">
         <v>58</v>
       </c>
       <c r="E39" s="1"/>
@@ -6275,13 +6288,13 @@
         <v>77</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="H39" s="57" t="s">
+      <c r="H39" s="55" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="24"/>
-      <c r="B40" s="42"/>
+      <c r="B40" s="41"/>
       <c r="C40" s="1"/>
       <c r="D40" s="2" t="s">
         <v>15</v>
@@ -6295,7 +6308,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="24"/>
-      <c r="B41" s="42"/>
+      <c r="B41" s="41"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
         <v>79</v>
@@ -6309,9 +6322,9 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="24"/>
-      <c r="B42" s="42"/>
+      <c r="B42" s="41"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="39" t="s">
+      <c r="D42" s="38" t="s">
         <v>74</v>
       </c>
       <c r="E42" s="1"/>
@@ -6321,7 +6334,7 @@
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="20"/>
-      <c r="B43" s="43"/>
+      <c r="B43" s="42"/>
       <c r="C43" s="22"/>
       <c r="D43" s="35" t="s">
         <v>81</v>
@@ -6399,13 +6412,13 @@
       <c r="A49" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="B49" s="49" t="s">
+      <c r="B49" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="C49" s="49" t="s">
+      <c r="C49" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="49" t="s">
+      <c r="D49" s="47" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="18"/>
@@ -6415,13 +6428,13 @@
     </row>
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="30"/>
-      <c r="B50" s="48" t="s">
+      <c r="B50" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="C50" s="48" t="s">
+      <c r="C50" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="D50" s="48" t="s">
+      <c r="D50" s="46" t="s">
         <v>85</v>
       </c>
       <c r="E50" s="1"/>
@@ -6439,7 +6452,7 @@
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
       <c r="G51" s="18"/>
-      <c r="H51" s="54" t="s">
+      <c r="H51" s="52" t="s">
         <v>43</v>
       </c>
     </row>
@@ -6451,7 +6464,7 @@
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
       <c r="G52" s="22"/>
-      <c r="H52" s="55" t="s">
+      <c r="H52" s="53" t="s">
         <v>91</v>
       </c>
     </row>
@@ -6515,7 +6528,7 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-      <c r="H57" s="56" t="s">
+      <c r="H57" s="54" t="s">
         <v>43</v>
       </c>
     </row>
@@ -6527,7 +6540,7 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
-      <c r="H58" s="57" t="s">
+      <c r="H58" s="55" t="s">
         <v>95</v>
       </c>
     </row>
@@ -6563,7 +6576,7 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="56" t="s">
+      <c r="H61" s="54" t="s">
         <v>43</v>
       </c>
     </row>
@@ -6575,7 +6588,7 @@
       <c r="E62" s="22"/>
       <c r="F62" s="22"/>
       <c r="G62" s="22"/>
-      <c r="H62" s="55" t="s">
+      <c r="H62" s="53" t="s">
         <v>97</v>
       </c>
     </row>
@@ -6611,7 +6624,7 @@
       <c r="G64" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="H64" s="19" t="s">
+      <c r="H64" s="36" t="s">
         <v>69</v>
       </c>
     </row>
@@ -6620,27 +6633,27 @@
       <c r="B65" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C65" s="38" t="s">
+      <c r="C65" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="38" t="s">
+      <c r="D65" s="37" t="s">
         <v>91</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>101</v>
       </c>
       <c r="F65" s="1"/>
-      <c r="G65" s="38" t="s">
+      <c r="G65" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H65" s="25" t="s">
+      <c r="H65" s="39" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="24"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="47" t="s">
+      <c r="C66" s="45" t="s">
         <v>28</v>
       </c>
       <c r="D66" s="2" t="s">
@@ -6648,15 +6661,15 @@
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="39" t="s">
+      <c r="G66" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="H66" s="25"/>
+      <c r="H66" s="39"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="24"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="48" t="s">
+      <c r="C67" s="46" t="s">
         <v>85</v>
       </c>
       <c r="D67" s="1" t="s">
@@ -6664,62 +6677,62 @@
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="38" t="s">
+      <c r="G67" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="H67" s="25"/>
+      <c r="H67" s="39"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="24"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="48"/>
-      <c r="D68" s="47" t="s">
+      <c r="C68" s="46"/>
+      <c r="D68" s="45" t="s">
         <v>28</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="39" t="s">
+      <c r="G68" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="H68" s="25"/>
+      <c r="H68" s="39"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="24"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="48"/>
-      <c r="D69" s="48" t="s">
+      <c r="C69" s="46"/>
+      <c r="D69" s="46" t="s">
         <v>31</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="38" t="s">
+      <c r="G69" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="H69" s="25"/>
+      <c r="H69" s="39"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="24"/>
       <c r="B70" s="1"/>
-      <c r="C70" s="48"/>
-      <c r="D70" s="48"/>
+      <c r="C70" s="46"/>
+      <c r="D70" s="46"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="58" t="s">
+      <c r="G70" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="H70" s="25"/>
+      <c r="H70" s="39"/>
     </row>
     <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="30"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="48"/>
-      <c r="D71" s="48"/>
+      <c r="C71" s="46"/>
+      <c r="D71" s="46"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="59" t="s">
+      <c r="G71" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="H71" s="25"/>
+      <c r="H71" s="39"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
@@ -6795,7 +6808,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="24"/>
-      <c r="B76" s="44" t="s">
+      <c r="B76" s="43" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="1"/>
@@ -6809,7 +6822,7 @@
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="20"/>
-      <c r="B77" s="43" t="s">
+      <c r="B77" s="42" t="s">
         <v>115</v>
       </c>
       <c r="C77" s="22"/>
@@ -6825,7 +6838,7 @@
       <c r="A78" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="B78" s="48" t="s">
+      <c r="B78" s="46" t="s">
         <v>28</v>
       </c>
       <c r="C78" s="1"/>
@@ -6839,7 +6852,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="24"/>
-      <c r="B79" s="48" t="s">
+      <c r="B79" s="46" t="s">
         <v>85</v>
       </c>
       <c r="C79" s="1"/>
@@ -6853,31 +6866,31 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="24"/>
-      <c r="B80" s="48"/>
+      <c r="B80" s="46"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="58" t="s">
+      <c r="G80" s="56" t="s">
         <v>43</v>
       </c>
       <c r="H80" s="25"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="24"/>
-      <c r="B81" s="48"/>
+      <c r="B81" s="46"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="59" t="s">
+      <c r="G81" s="57" t="s">
         <v>91</v>
       </c>
       <c r="H81" s="25"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="24"/>
-      <c r="B82" s="48"/>
+      <c r="B82" s="46"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -6889,7 +6902,7 @@
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="20"/>
-      <c r="B83" s="50"/>
+      <c r="B83" s="48"/>
       <c r="C83" s="22"/>
       <c r="D83" s="22"/>
       <c r="E83" s="22"/>
@@ -6946,7 +6959,7 @@
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="38" t="s">
+      <c r="G87" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H87" s="25"/>
@@ -6958,7 +6971,7 @@
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
-      <c r="G88" s="39" t="s">
+      <c r="G88" s="38" t="s">
         <v>12</v>
       </c>
       <c r="H88" s="25"/>
@@ -6999,7 +7012,7 @@
         <v>15</v>
       </c>
       <c r="E91" s="18"/>
-      <c r="F91" s="41" t="s">
+      <c r="F91" s="40" t="s">
         <v>29</v>
       </c>
       <c r="G91" s="18"/>
@@ -7015,7 +7028,7 @@
         <v>16</v>
       </c>
       <c r="E92" s="22"/>
-      <c r="F92" s="43" t="s">
+      <c r="F92" s="42" t="s">
         <v>126</v>
       </c>
       <c r="G92" s="22"/>
@@ -7839,13 +7852,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6EC8FFF-5362-4FBB-81C5-0CE8BAD24C7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8F6C438-A15A-4C89-91F4-58B83B61C682}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38A3F63F-2F60-43C0-8654-FD02CB6B1CD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D3BE358-601C-4399-86C5-69B11AA2ED05}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D517EF44-A622-466A-86B4-50F7F9D79E76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5F73B29-8E6B-4B7B-8C47-AC6D8321E5BA}"/>
 </file>
--- a/Plannings 2026 S16.xlsx
+++ b/Plannings 2026 S16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3A5B07A-8FED-4E31-BA69-31D742EA78EE}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{907AB746-E65D-47C2-B5C9-D6A18048B3FC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="150">
   <si>
     <t>Planning des salariés du 13/04/2026 au 19/04/2026</t>
   </si>
@@ -453,10 +453,25 @@
     <t>LOUIBA Yacine</t>
   </si>
   <si>
-    <t xml:space="preserve">C. PADEL // </t>
-  </si>
-  <si>
     <t>P50M // ANIV</t>
+  </si>
+  <si>
+    <t>C. PADEL // EDF // CUP PADEL</t>
+  </si>
+  <si>
+    <t>C. PADEL // P50 // EDF // LEAGUES</t>
+  </si>
+  <si>
+    <t>C. PADEL // EDF // LEAGUES</t>
+  </si>
+  <si>
+    <t>C. PADEL // EDF // LEAGUES // TOURNOI IGENSIA</t>
+  </si>
+  <si>
+    <t>C. PADEL // INAUGURATION PADEL</t>
+  </si>
+  <si>
+    <t>EDF // ANIV</t>
   </si>
 </sst>
 </file>
@@ -5685,15 +5700,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="H3" s="15" t="s">
         <v>143</v>
-      </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7852,13 +7877,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8F6C438-A15A-4C89-91F4-58B83B61C682}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32580FCE-F097-488B-B429-5F6D0081D329}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D3BE358-601C-4399-86C5-69B11AA2ED05}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{419BD65C-F621-4F37-8B71-2C5B9C19DB27}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5F73B29-8E6B-4B7B-8C47-AC6D8321E5BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A89076BB-658D-4B8F-8E56-2A65F8DB8100}"/>
 </file>
--- a/Plannings 2026 S16.xlsx
+++ b/Plannings 2026 S16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{907AB746-E65D-47C2-B5C9-D6A18048B3FC}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A11DB12E-41F3-4A52-8AFB-1FC127432AFE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5670,10 +5670,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="40.140625" customWidth="1"/>
+    <col min="1" max="8" width="48.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7085,7 +7088,7 @@
       <c r="G94" s="22"/>
       <c r="H94" s="23"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="32"/>
       <c r="C95" s="32"/>
       <c r="D95" s="32"/>
@@ -7128,7 +7131,8 @@
     <mergeCell ref="A9:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="33" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7877,13 +7881,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32580FCE-F097-488B-B429-5F6D0081D329}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{818E86A5-F5EA-4119-9955-C95B5A21FA8C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{419BD65C-F621-4F37-8B71-2C5B9C19DB27}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A229E62-260D-48FB-941B-1FC4CE57FFA1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A89076BB-658D-4B8F-8E56-2A65F8DB8100}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A2781D-D577-4B30-9A10-4D3F148A4425}"/>
 </file>
--- a/Plannings 2026 S16.xlsx
+++ b/Plannings 2026 S16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A11DB12E-41F3-4A52-8AFB-1FC127432AFE}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FD16D83-841A-4024-ABAE-EB41FA720CC5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -462,16 +462,16 @@
     <t>C. PADEL // P50 // EDF // LEAGUES</t>
   </si>
   <si>
-    <t>C. PADEL // EDF // LEAGUES</t>
-  </si>
-  <si>
-    <t>C. PADEL // EDF // LEAGUES // TOURNOI IGENSIA</t>
-  </si>
-  <si>
     <t>C. PADEL // INAUGURATION PADEL</t>
   </si>
   <si>
     <t>EDF // ANIV</t>
+  </si>
+  <si>
+    <t>C. PADEL // EDF // LEAGUES // LDC : LIVERPOOL-PSG</t>
+  </si>
+  <si>
+    <t>C. PADEL // EDF // LEAGUES // LDC : BAYERN-REAL // TOURNOI IGENSIA</t>
   </si>
 </sst>
 </file>
@@ -867,7 +867,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -902,19 +902,7 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -926,9 +914,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -938,34 +923,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1043,14 +1007,56 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5680,150 +5686,150 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="15" t="s">
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+    </row>
+    <row r="3" spans="1:8" s="62" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B3" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="63" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="63" t="s">
         <v>146</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="F3" s="63" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" s="63" t="s">
         <v>147</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="63" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="34" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="19"/>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="35" t="s">
+      <c r="A6" s="55"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="23"/>
+      <c r="H6" s="18"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="15"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22" t="s">
+      <c r="A8" s="55"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="23"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="19"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="15"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
+      <c r="A10" s="54"/>
       <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
@@ -5838,180 +5844,180 @@
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="25"/>
+      <c r="H10" s="19"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" s="45" t="s">
+      <c r="A11" s="54"/>
+      <c r="B11" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="45" t="s">
+      <c r="D11" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="31" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="25"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="46" t="s">
+      <c r="A12" s="54"/>
+      <c r="B12" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="25"/>
+      <c r="H12" s="19"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="43" t="s">
+      <c r="D13" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="41"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="25"/>
+      <c r="H13" s="19"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20"/>
-      <c r="B14" s="22" t="s">
+      <c r="A14" s="55"/>
+      <c r="B14" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="42" t="s">
+      <c r="D14" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="42"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="23"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18" t="s">
+      <c r="B15" s="14"/>
+      <c r="C15" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="44" t="s">
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="32" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="20"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22" t="s">
+      <c r="A16" s="55"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="61" t="s">
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="49" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="29"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="52"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="18"/>
-      <c r="H18" s="19"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="20"/>
-      <c r="B19" s="22" t="s">
+      <c r="A19" s="55"/>
+      <c r="B19" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="23"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18" t="s">
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18" t="s">
+      <c r="E20" s="14"/>
+      <c r="F20" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="58" t="s">
+      <c r="G20" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="19"/>
+      <c r="H20" s="15"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
+      <c r="A21" s="54"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
@@ -6021,13 +6027,13 @@
       <c r="F21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G21" s="57" t="s">
+      <c r="G21" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="H21" s="25"/>
+      <c r="H21" s="19"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
+      <c r="A22" s="54"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -6036,10 +6042,10 @@
       <c r="G22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H22" s="25"/>
+      <c r="H22" s="19"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="30"/>
+      <c r="A23" s="57"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -6048,225 +6054,225 @@
       <c r="G23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="25"/>
+      <c r="H23" s="19"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="50" t="s">
+      <c r="B24" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="C24" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="34" t="s">
+      <c r="D24" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="40" t="s">
+      <c r="E24" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="59" t="s">
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="47" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="51" t="s">
+      <c r="A25" s="54"/>
+      <c r="B25" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D25" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="E25" s="41" t="s">
+      <c r="E25" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="60" t="s">
+      <c r="H25" s="48" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
+      <c r="A26" s="54"/>
       <c r="B26" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="D26" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="41"/>
+      <c r="E26" s="29"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="31" t="s">
+      <c r="H26" s="21" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
+      <c r="A27" s="54"/>
       <c r="B27" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D27" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="41"/>
+      <c r="E27" s="29"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="25" t="s">
+      <c r="H27" s="19" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="43" t="s">
+      <c r="A28" s="54"/>
+      <c r="B28" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="49" t="s">
+      <c r="C28" s="37" t="s">
         <v>49</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="41"/>
+      <c r="E28" s="29"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="25"/>
+      <c r="H28" s="19"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="41" t="s">
+      <c r="A29" s="54"/>
+      <c r="B29" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="39" t="s">
         <v>61</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="41"/>
+      <c r="E29" s="29"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="25"/>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-      <c r="B30" s="38" t="s">
+      <c r="A30" s="54"/>
+      <c r="B30" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="49" t="s">
+      <c r="D30" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="E30" s="41"/>
+      <c r="E30" s="29"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="25"/>
+      <c r="H30" s="19"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="24"/>
-      <c r="B31" s="37" t="s">
+      <c r="A31" s="54"/>
+      <c r="B31" s="25" t="s">
         <v>63</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="51" t="s">
+      <c r="D31" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="E31" s="41"/>
+      <c r="E31" s="29"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="25"/>
+      <c r="H31" s="19"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="24"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="49" t="s">
+      <c r="A32" s="54"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="D32" s="37"/>
-      <c r="E32" s="41"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="29"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="25"/>
+      <c r="H32" s="19"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="20"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35" t="s">
+      <c r="A33" s="55"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="35"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="18"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="34" t="s">
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H34" s="19"/>
+      <c r="H34" s="15"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="20"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="35" t="s">
+      <c r="A35" s="55"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H35" s="23"/>
+      <c r="H35" s="18"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="34" t="s">
+      <c r="B36" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18" t="s">
+      <c r="C36" s="14"/>
+      <c r="D36" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="34" t="s">
+      <c r="F36" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="18"/>
-      <c r="H36" s="36" t="s">
+      <c r="G36" s="14"/>
+      <c r="H36" s="24" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
-      <c r="B37" s="37" t="s">
+      <c r="A37" s="54"/>
+      <c r="B37" s="25" t="s">
         <v>20</v>
       </c>
       <c r="C37" s="1"/>
@@ -6276,21 +6282,21 @@
       <c r="E37" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F37" s="37" t="s">
+      <c r="F37" s="25" t="s">
         <v>20</v>
       </c>
       <c r="G37" s="1"/>
-      <c r="H37" s="39" t="s">
+      <c r="H37" s="27" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="24"/>
-      <c r="B38" s="43" t="s">
+      <c r="A38" s="54"/>
+      <c r="B38" s="31" t="s">
         <v>73</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="38" t="s">
+      <c r="D38" s="26" t="s">
         <v>74</v>
       </c>
       <c r="E38" s="1"/>
@@ -6298,17 +6304,17 @@
         <v>15</v>
       </c>
       <c r="G38" s="1"/>
-      <c r="H38" s="54" t="s">
+      <c r="H38" s="42" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="41" t="s">
+      <c r="A39" s="54"/>
+      <c r="B39" s="29" t="s">
         <v>76</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="37" t="s">
+      <c r="D39" s="25" t="s">
         <v>58</v>
       </c>
       <c r="E39" s="1"/>
@@ -6316,13 +6322,13 @@
         <v>77</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="H39" s="55" t="s">
+      <c r="H39" s="43" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
-      <c r="B40" s="41"/>
+      <c r="A40" s="54"/>
+      <c r="B40" s="29"/>
       <c r="C40" s="1"/>
       <c r="D40" s="2" t="s">
         <v>15</v>
@@ -6330,13 +6336,13 @@
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="31" t="s">
+      <c r="H40" s="21" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="41"/>
+      <c r="A41" s="54"/>
+      <c r="B41" s="29"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
         <v>79</v>
@@ -6344,344 +6350,344 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="25" t="s">
+      <c r="H41" s="19" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="24"/>
-      <c r="B42" s="41"/>
+      <c r="A42" s="54"/>
+      <c r="B42" s="29"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="38" t="s">
+      <c r="D42" s="26" t="s">
         <v>74</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="25"/>
+      <c r="H42" s="19"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="20"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="35" t="s">
+      <c r="A43" s="55"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="23"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="18"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18" t="s">
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="19"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="15"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="20"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22" t="s">
+      <c r="A45" s="55"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="23"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="18"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="26" t="s">
+      <c r="A46" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="29"/>
+      <c r="B46" s="50"/>
+      <c r="C46" s="51"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="52"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="B47" s="18"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="19" t="s">
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="20"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="23" t="s">
+      <c r="A48" s="55"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="18" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C49" s="47" t="s">
+      <c r="C49" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="47" t="s">
+      <c r="D49" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="19"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="15"/>
     </row>
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="30"/>
-      <c r="B50" s="46" t="s">
+      <c r="A50" s="57"/>
+      <c r="B50" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="C50" s="46" t="s">
+      <c r="C50" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="D50" s="46" t="s">
+      <c r="D50" s="34" t="s">
         <v>85</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="25"/>
+      <c r="H50" s="19"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="52" t="s">
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="40" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="20"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="53" t="s">
+      <c r="A52" s="55"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="41" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="B53" s="18"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="34" t="s">
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G53" s="18"/>
-      <c r="H53" s="19"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="15"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="20"/>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="35" t="s">
+      <c r="A54" s="55"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G54" s="22"/>
-      <c r="H54" s="23"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="18"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="19" t="s">
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="24"/>
+      <c r="A56" s="54"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
-      <c r="H56" s="25" t="s">
+      <c r="H56" s="19" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="24"/>
+      <c r="A57" s="54"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-      <c r="H57" s="54" t="s">
+      <c r="H57" s="42" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="24"/>
+      <c r="A58" s="54"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
-      <c r="H58" s="55" t="s">
+      <c r="H58" s="43" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="24"/>
+      <c r="A59" s="54"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
-      <c r="H59" s="31" t="s">
+      <c r="H59" s="21" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="24"/>
+      <c r="A60" s="54"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="25" t="s">
+      <c r="H60" s="19" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="24"/>
+      <c r="A61" s="54"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="54" t="s">
+      <c r="H61" s="42" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="20"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="53" t="s">
+      <c r="A62" s="55"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="41" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="26" t="s">
+      <c r="A63" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="B63" s="27"/>
-      <c r="C63" s="28"/>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="29"/>
+      <c r="B63" s="50"/>
+      <c r="C63" s="51"/>
+      <c r="D63" s="51"/>
+      <c r="E63" s="51"/>
+      <c r="F63" s="51"/>
+      <c r="G63" s="51"/>
+      <c r="H63" s="52"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="16" t="s">
+      <c r="A64" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="B64" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="34" t="s">
+      <c r="C64" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D64" s="34" t="s">
+      <c r="D64" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E64" s="18" t="s">
+      <c r="E64" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F64" s="18"/>
-      <c r="G64" s="34" t="s">
+      <c r="F64" s="14"/>
+      <c r="G64" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H64" s="36" t="s">
+      <c r="H64" s="24" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="24"/>
+      <c r="A65" s="54"/>
       <c r="B65" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C65" s="37" t="s">
+      <c r="C65" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="37" t="s">
+      <c r="D65" s="25" t="s">
         <v>91</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>101</v>
       </c>
       <c r="F65" s="1"/>
-      <c r="G65" s="37" t="s">
+      <c r="G65" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="H65" s="39" t="s">
+      <c r="H65" s="27" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="24"/>
+      <c r="A66" s="54"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="45" t="s">
+      <c r="C66" s="33" t="s">
         <v>28</v>
       </c>
       <c r="D66" s="2" t="s">
@@ -6689,15 +6695,15 @@
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="38" t="s">
+      <c r="G66" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="H66" s="39"/>
+      <c r="H66" s="27"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="24"/>
+      <c r="A67" s="54"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="46" t="s">
+      <c r="C67" s="34" t="s">
         <v>85</v>
       </c>
       <c r="D67" s="1" t="s">
@@ -6705,117 +6711,117 @@
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="37" t="s">
+      <c r="G67" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="H67" s="39"/>
+      <c r="H67" s="27"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="24"/>
+      <c r="A68" s="54"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="46"/>
-      <c r="D68" s="45" t="s">
+      <c r="C68" s="34"/>
+      <c r="D68" s="33" t="s">
         <v>28</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="38" t="s">
+      <c r="G68" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="H68" s="39"/>
+      <c r="H68" s="27"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="24"/>
+      <c r="A69" s="54"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="46"/>
-      <c r="D69" s="46" t="s">
+      <c r="C69" s="34"/>
+      <c r="D69" s="34" t="s">
         <v>31</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="37" t="s">
+      <c r="G69" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="H69" s="39"/>
+      <c r="H69" s="27"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="24"/>
+      <c r="A70" s="54"/>
       <c r="B70" s="1"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
+      <c r="C70" s="34"/>
+      <c r="D70" s="34"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="56" t="s">
+      <c r="G70" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="H70" s="39"/>
+      <c r="H70" s="27"/>
     </row>
     <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="30"/>
+      <c r="A71" s="57"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="46"/>
-      <c r="D71" s="46"/>
+      <c r="C71" s="34"/>
+      <c r="D71" s="34"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="57" t="s">
+      <c r="G71" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="H71" s="39"/>
+      <c r="H71" s="27"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="B72" s="18"/>
-      <c r="C72" s="34" t="s">
+      <c r="B72" s="14"/>
+      <c r="C72" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
-      <c r="F72" s="34" t="s">
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G72" s="18"/>
-      <c r="H72" s="19"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="15"/>
     </row>
     <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="20"/>
-      <c r="B73" s="22"/>
-      <c r="C73" s="35" t="s">
+      <c r="A73" s="55"/>
+      <c r="B73" s="17"/>
+      <c r="C73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D73" s="22"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="35" t="s">
+      <c r="D73" s="17"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G73" s="22"/>
-      <c r="H73" s="23"/>
+      <c r="G73" s="17"/>
+      <c r="H73" s="18"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="16" t="s">
+      <c r="A74" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="B74" s="18" t="s">
+      <c r="B74" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C74" s="18" t="s">
+      <c r="C74" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D74" s="18"/>
-      <c r="E74" s="18" t="s">
+      <c r="D74" s="14"/>
+      <c r="E74" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F74" s="18" t="s">
+      <c r="F74" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G74" s="18" t="s">
+      <c r="G74" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="H74" s="19"/>
+      <c r="H74" s="15"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="24"/>
+      <c r="A75" s="54"/>
       <c r="B75" s="1" t="s">
         <v>111</v>
       </c>
@@ -6832,11 +6838,11 @@
       <c r="G75" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H75" s="25"/>
+      <c r="H75" s="19"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="24"/>
-      <c r="B76" s="43" t="s">
+      <c r="A76" s="54"/>
+      <c r="B76" s="31" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="1"/>
@@ -6846,27 +6852,27 @@
       <c r="G76" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H76" s="25"/>
+      <c r="H76" s="19"/>
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="20"/>
-      <c r="B77" s="42" t="s">
+      <c r="A77" s="55"/>
+      <c r="B77" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="C77" s="22"/>
-      <c r="D77" s="22"/>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
-      <c r="G77" s="22" t="s">
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="H77" s="23"/>
+      <c r="H77" s="18"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="33" t="s">
+      <c r="A78" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="B78" s="46" t="s">
+      <c r="B78" s="34" t="s">
         <v>28</v>
       </c>
       <c r="C78" s="1"/>
@@ -6876,11 +6882,11 @@
       <c r="G78" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H78" s="25"/>
+      <c r="H78" s="19"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="24"/>
-      <c r="B79" s="46" t="s">
+      <c r="A79" s="54"/>
+      <c r="B79" s="34" t="s">
         <v>85</v>
       </c>
       <c r="C79" s="1"/>
@@ -6890,35 +6896,35 @@
       <c r="G79" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H79" s="25"/>
+      <c r="H79" s="19"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="24"/>
-      <c r="B80" s="46"/>
+      <c r="A80" s="54"/>
+      <c r="B80" s="34"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="56" t="s">
+      <c r="G80" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="H80" s="25"/>
+      <c r="H80" s="19"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="24"/>
-      <c r="B81" s="46"/>
+      <c r="A81" s="54"/>
+      <c r="B81" s="34"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="57" t="s">
+      <c r="G81" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="H81" s="25"/>
+      <c r="H81" s="19"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="24"/>
-      <c r="B82" s="46"/>
+      <c r="A82" s="54"/>
+      <c r="B82" s="34"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -6926,184 +6932,188 @@
       <c r="G82" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H82" s="25"/>
+      <c r="H82" s="19"/>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="20"/>
-      <c r="B83" s="48"/>
-      <c r="C83" s="22"/>
-      <c r="D83" s="22"/>
-      <c r="E83" s="22"/>
-      <c r="F83" s="22"/>
-      <c r="G83" s="22" t="s">
+      <c r="A83" s="55"/>
+      <c r="B83" s="36"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="17"/>
+      <c r="G83" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="H83" s="23"/>
+      <c r="H83" s="18"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="16" t="s">
+      <c r="A84" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="B84" s="18"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="34" t="s">
+      <c r="B84" s="14"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E84" s="18"/>
-      <c r="F84" s="18"/>
-      <c r="G84" s="18"/>
-      <c r="H84" s="19"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="15"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="20"/>
-      <c r="B85" s="22"/>
-      <c r="C85" s="22"/>
-      <c r="D85" s="35" t="s">
+      <c r="A85" s="55"/>
+      <c r="B85" s="17"/>
+      <c r="C85" s="17"/>
+      <c r="D85" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="E85" s="22"/>
-      <c r="F85" s="22"/>
-      <c r="G85" s="22"/>
-      <c r="H85" s="23"/>
+      <c r="E85" s="17"/>
+      <c r="F85" s="17"/>
+      <c r="G85" s="17"/>
+      <c r="H85" s="18"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="16" t="s">
+      <c r="A86" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="B86" s="18"/>
-      <c r="C86" s="18"/>
-      <c r="D86" s="18"/>
-      <c r="E86" s="18"/>
-      <c r="F86" s="18"/>
-      <c r="G86" s="34" t="s">
+      <c r="B86" s="14"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H86" s="19"/>
+      <c r="H86" s="15"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="24"/>
+      <c r="A87" s="54"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="37" t="s">
+      <c r="G87" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H87" s="25"/>
+      <c r="H87" s="19"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="24"/>
+      <c r="A88" s="54"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
-      <c r="G88" s="38" t="s">
+      <c r="G88" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="H88" s="25"/>
+      <c r="H88" s="19"/>
     </row>
     <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="20"/>
-      <c r="B89" s="22"/>
-      <c r="C89" s="22"/>
-      <c r="D89" s="22"/>
-      <c r="E89" s="22"/>
-      <c r="F89" s="22"/>
-      <c r="G89" s="35" t="s">
+      <c r="A89" s="55"/>
+      <c r="B89" s="17"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="17"/>
+      <c r="E89" s="17"/>
+      <c r="F89" s="17"/>
+      <c r="G89" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="H89" s="23"/>
+      <c r="H89" s="18"/>
     </row>
     <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="26" t="s">
+      <c r="A90" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="B90" s="27"/>
-      <c r="C90" s="28"/>
-      <c r="D90" s="28"/>
-      <c r="E90" s="28"/>
-      <c r="F90" s="28"/>
-      <c r="G90" s="28"/>
-      <c r="H90" s="29"/>
+      <c r="B90" s="50"/>
+      <c r="C90" s="51"/>
+      <c r="D90" s="51"/>
+      <c r="E90" s="51"/>
+      <c r="F90" s="51"/>
+      <c r="G90" s="51"/>
+      <c r="H90" s="52"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="B91" s="18"/>
-      <c r="C91" s="18" t="s">
+      <c r="B91" s="14"/>
+      <c r="C91" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D91" s="18" t="s">
+      <c r="D91" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E91" s="18"/>
-      <c r="F91" s="40" t="s">
+      <c r="E91" s="14"/>
+      <c r="F91" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="G91" s="18"/>
-      <c r="H91" s="19"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="15"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="20"/>
-      <c r="B92" s="22"/>
-      <c r="C92" s="22" t="s">
+      <c r="A92" s="55"/>
+      <c r="B92" s="17"/>
+      <c r="C92" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="D92" s="22" t="s">
+      <c r="D92" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E92" s="22"/>
-      <c r="F92" s="42" t="s">
+      <c r="E92" s="17"/>
+      <c r="F92" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="G92" s="22"/>
-      <c r="H92" s="23"/>
+      <c r="G92" s="17"/>
+      <c r="H92" s="18"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="16" t="s">
+      <c r="A93" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="B93" s="18"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="34" t="s">
+      <c r="B93" s="14"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E93" s="18"/>
-      <c r="F93" s="18"/>
-      <c r="G93" s="18"/>
-      <c r="H93" s="19"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="H93" s="15"/>
     </row>
     <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="20"/>
-      <c r="B94" s="22"/>
-      <c r="C94" s="22"/>
-      <c r="D94" s="35" t="s">
+      <c r="A94" s="55"/>
+      <c r="B94" s="17"/>
+      <c r="C94" s="17"/>
+      <c r="D94" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="E94" s="22"/>
-      <c r="F94" s="22"/>
-      <c r="G94" s="22"/>
-      <c r="H94" s="23"/>
+      <c r="E94" s="17"/>
+      <c r="F94" s="17"/>
+      <c r="G94" s="17"/>
+      <c r="H94" s="18"/>
     </row>
     <row r="95" spans="1:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="32"/>
-      <c r="C95" s="32"/>
-      <c r="D95" s="32"/>
-      <c r="E95" s="32"/>
-      <c r="F95" s="32"/>
-      <c r="G95" s="32"/>
-      <c r="H95" s="32"/>
+      <c r="B95" s="56"/>
+      <c r="C95" s="56"/>
+      <c r="D95" s="56"/>
+      <c r="E95" s="56"/>
+      <c r="F95" s="56"/>
+      <c r="G95" s="56"/>
+      <c r="H95" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B63:H63"/>
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="B2:H2"/>
     <mergeCell ref="A91:A92"/>
     <mergeCell ref="A93:A94"/>
     <mergeCell ref="B95:H95"/>
@@ -7112,6 +7122,11 @@
     <mergeCell ref="A74:A77"/>
     <mergeCell ref="A78:A83"/>
     <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="A86:A89"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="A51:A52"/>
     <mergeCell ref="A53:A54"/>
@@ -7120,15 +7135,6 @@
     <mergeCell ref="A36:A43"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="33" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -7147,20 +7153,20 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="61" t="s">
         <v>129</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -7716,6 +7722,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F57AE488C1C9C348AE667C65EC1B6349" ma:contentTypeVersion="83" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="584bf6b77295f7da4f9cf4ac656056b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3c298670-db79-47a5-968d-a4570c34317f" xmlns:ns3="17e8e7ea-beb0-4155-adc4-5bfa61f32508" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0744868ac059cd1623b27209cff1bde4" ns2:_="" ns3:_="">
     <xsd:import namespace="3c298670-db79-47a5-968d-a4570c34317f"/>
@@ -7860,15 +7875,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7881,13 +7887,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{818E86A5-F5EA-4119-9955-C95B5A21FA8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A229E62-260D-48FB-941B-1FC4CE57FFA1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A229E62-260D-48FB-941B-1FC4CE57FFA1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{818E86A5-F5EA-4119-9955-C95B5A21FA8C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A2781D-D577-4B30-9A10-4D3F148A4425}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A2781D-D577-4B30-9A10-4D3F148A4425}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Plannings 2026 S16.xlsx
+++ b/Plannings 2026 S16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FD16D83-841A-4024-ABAE-EB41FA720CC5}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7BDFEA3-BF96-4147-B5B1-379671B0AC15}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="151">
   <si>
     <t>Planning des salariés du 13/04/2026 au 19/04/2026</t>
   </si>
@@ -210,18 +210,12 @@
     <t>14:15/16:45</t>
   </si>
   <si>
-    <t>15:45/17:00</t>
-  </si>
-  <si>
     <t>18:00/21:15</t>
   </si>
   <si>
     <t>16:45/17:45</t>
   </si>
   <si>
-    <t>17:00/20:30</t>
-  </si>
-  <si>
     <t>17:45/21:15</t>
   </si>
   <si>
@@ -472,6 +466,15 @@
   </si>
   <si>
     <t>C. PADEL // EDF // LEAGUES // LDC : BAYERN-REAL // TOURNOI IGENSIA</t>
+  </si>
+  <si>
+    <t>15:45/17:30</t>
+  </si>
+  <si>
+    <t>17:30/20:30</t>
+  </si>
+  <si>
+    <t>18h45/20:30</t>
   </si>
 </sst>
 </file>
@@ -2803,13 +2806,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2847,13 +2850,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2891,21 +2894,1649 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2933,23 +4564,551 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2977,23 +5136,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3023,21 +5226,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB3C0959-561A-424C-8F34-0D5E0F21F5E3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3053,7 +5256,51 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
+          <a:off x="8041821" y="979714"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88CA5A6A-9453-477E-895D-3F528B2093C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10722429" y="1755321"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3067,2237 +5314,37 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB3C0959-561A-424C-8F34-0D5E0F21F5E3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8041821" y="979714"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88CA5A6A-9453-477E-895D-3F528B2093C6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10722429" y="1755321"/>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBBB8A6D-5DB9-4041-BF37-9B1BE859B8DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3252107" y="5769429"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5679,7 +5726,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="48.7109375" customWidth="1"/>
@@ -5709,25 +5756,25 @@
     </row>
     <row r="3" spans="1:8" s="62" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>147</v>
+      </c>
+      <c r="E3" s="63" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" s="63" t="s">
+        <v>142</v>
+      </c>
+      <c r="G3" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="63" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" s="63" t="s">
-        <v>149</v>
-      </c>
-      <c r="E3" s="63" t="s">
-        <v>146</v>
-      </c>
-      <c r="F3" s="63" t="s">
-        <v>144</v>
-      </c>
-      <c r="G3" s="63" t="s">
-        <v>147</v>
-      </c>
       <c r="H3" s="63" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6159,7 +6206,7 @@
         <v>61</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="E29" s="29"/>
       <c r="F29" s="1"/>
@@ -6185,13 +6232,13 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="54"/>
       <c r="B31" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="D31" s="39" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="E31" s="29"/>
       <c r="F31" s="1"/>
@@ -6204,317 +6251,315 @@
       <c r="C32" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="D32" s="25"/>
+      <c r="D32" s="26" t="s">
+        <v>49</v>
+      </c>
       <c r="E32" s="29"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="19"/>
     </row>
-    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="55"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="23"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="18"/>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="57"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="E33" s="29"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="19"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H34" s="15"/>
+      <c r="A34" s="57"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="55"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="23"/>
+      <c r="E35" s="30"/>
       <c r="F35" s="17"/>
-      <c r="G35" s="23" t="s">
-        <v>13</v>
-      </c>
+      <c r="G35" s="17"/>
       <c r="H35" s="18"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B36" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14" t="s">
+      <c r="H36" s="15"/>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="55"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="18"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E38" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="22" t="s">
+      <c r="F38" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="14"/>
-      <c r="H36" s="24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="54"/>
-      <c r="B37" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F37" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="27" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="54"/>
-      <c r="B38" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" s="1"/>
-      <c r="H38" s="42" t="s">
-        <v>75</v>
+      <c r="G38" s="14"/>
+      <c r="H38" s="24" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="54"/>
-      <c r="B39" s="29" t="s">
-        <v>76</v>
+      <c r="B39" s="25" t="s">
+        <v>20</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1" t="s">
-        <v>77</v>
+      <c r="D39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F39" s="25" t="s">
+        <v>20</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="H39" s="43" t="s">
-        <v>78</v>
+      <c r="H39" s="27" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="54"/>
-      <c r="B40" s="29"/>
+      <c r="B40" s="31" t="s">
+        <v>71</v>
+      </c>
       <c r="C40" s="1"/>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="21" t="s">
-        <v>15</v>
+      <c r="H40" s="42" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="54"/>
-      <c r="B41" s="29"/>
+      <c r="B41" s="29" t="s">
+        <v>74</v>
+      </c>
       <c r="C41" s="1"/>
-      <c r="D41" s="1" t="s">
-        <v>79</v>
+      <c r="D41" s="25" t="s">
+        <v>58</v>
       </c>
       <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
+      <c r="F41" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="G41" s="1"/>
-      <c r="H41" s="19" t="s">
-        <v>80</v>
+      <c r="H41" s="43" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="54"/>
       <c r="B42" s="29"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="26" t="s">
-        <v>74</v>
+      <c r="D42" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="19"/>
-    </row>
-    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="55"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="18"/>
+      <c r="H42" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="54"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="19" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="15"/>
+      <c r="A44" s="54"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="19"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="55"/>
-      <c r="B45" s="17"/>
+      <c r="B45" s="30"/>
       <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17" t="s">
-        <v>83</v>
-      </c>
+      <c r="D45" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="17"/>
       <c r="F45" s="17"/>
       <c r="G45" s="17"/>
       <c r="H45" s="18"/>
     </row>
-    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="B46" s="50"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="51"/>
-      <c r="G46" s="51"/>
-      <c r="H46" s="52"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="15" t="s">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14" t="s">
         <v>15</v>
       </c>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="15"/>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="55"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="55"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="18" t="s">
-        <v>89</v>
-      </c>
+      <c r="A48" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B48" s="50"/>
+      <c r="C48" s="51"/>
+      <c r="D48" s="51"/>
+      <c r="E48" s="51"/>
+      <c r="F48" s="51"/>
+      <c r="G48" s="51"/>
+      <c r="H48" s="52"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="B49" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="C49" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="D49" s="35" t="s">
-        <v>28</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
       <c r="G49" s="14"/>
-      <c r="H49" s="15"/>
+      <c r="H49" s="15" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="57"/>
-      <c r="B50" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C50" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="D50" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="19"/>
+      <c r="A50" s="55"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="18" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
+        <v>140</v>
+      </c>
+      <c r="B51" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="35" t="s">
+        <v>28</v>
+      </c>
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
       <c r="G51" s="14"/>
-      <c r="H51" s="40" t="s">
-        <v>43</v>
-      </c>
+      <c r="H51" s="15"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="55"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="41" t="s">
-        <v>91</v>
-      </c>
+      <c r="A52" s="57"/>
+      <c r="B52" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="19"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="53" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="22" t="s">
-        <v>12</v>
-      </c>
+      <c r="F53" s="14"/>
       <c r="G53" s="14"/>
-      <c r="H53" s="15"/>
+      <c r="H53" s="40" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="55"/>
@@ -6522,48 +6567,50 @@
       <c r="C54" s="17"/>
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
-      <c r="F54" s="23" t="s">
-        <v>20</v>
-      </c>
+      <c r="F54" s="17"/>
       <c r="G54" s="17"/>
-      <c r="H54" s="18"/>
+      <c r="H54" s="41" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="53" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
+      <c r="F55" s="22" t="s">
+        <v>12</v>
+      </c>
       <c r="G55" s="14"/>
-      <c r="H55" s="15" t="s">
+      <c r="H55" s="15"/>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="55"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="17"/>
+      <c r="H56" s="18"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="15" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="54"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="54"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="42" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -6574,8 +6621,8 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
-      <c r="H58" s="43" t="s">
-        <v>95</v>
+      <c r="H58" s="19" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -6586,8 +6633,8 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
-      <c r="H59" s="21" t="s">
-        <v>15</v>
+      <c r="H59" s="42" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -6598,8 +6645,8 @@
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="19" t="s">
-        <v>96</v>
+      <c r="H60" s="43" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -6610,137 +6657,133 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="42" t="s">
+      <c r="H61" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="54"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="54"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="42" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="55"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="41" t="s">
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="55"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="17"/>
+      <c r="H64" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="50"/>
+      <c r="C65" s="51"/>
+      <c r="D65" s="51"/>
+      <c r="E65" s="51"/>
+      <c r="F65" s="51"/>
+      <c r="G65" s="51"/>
+      <c r="H65" s="52"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="53" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="B63" s="50"/>
-      <c r="C63" s="51"/>
-      <c r="D63" s="51"/>
-      <c r="E63" s="51"/>
-      <c r="F63" s="51"/>
-      <c r="G63" s="51"/>
-      <c r="H63" s="52"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="B64" s="14" t="s">
+      <c r="B66" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="C66" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D64" s="22" t="s">
+      <c r="D66" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E64" s="14" t="s">
+      <c r="E66" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F64" s="14"/>
-      <c r="G64" s="22" t="s">
+      <c r="F66" s="14"/>
+      <c r="G66" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H64" s="24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="54"/>
-      <c r="B65" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C65" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="D65" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F65" s="1"/>
-      <c r="G65" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="H65" s="27" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="54"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H66" s="27"/>
+      <c r="H66" s="24" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="54"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E67" s="1"/>
+      <c r="B67" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="F67" s="1"/>
       <c r="G67" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="H67" s="27"/>
+        <v>100</v>
+      </c>
+      <c r="H67" s="27" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="54"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="34"/>
-      <c r="D68" s="33" t="s">
+      <c r="C68" s="33" t="s">
         <v>28</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="26" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="H68" s="27"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="54"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="34"/>
-      <c r="D69" s="34" t="s">
-        <v>31</v>
+      <c r="C69" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="25" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H69" s="27"/>
     </row>
@@ -6748,177 +6791,181 @@
       <c r="A70" s="54"/>
       <c r="B70" s="1"/>
       <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
+      <c r="D70" s="33" t="s">
+        <v>28</v>
+      </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="44" t="s">
-        <v>43</v>
+      <c r="G70" s="26" t="s">
+        <v>12</v>
       </c>
       <c r="H70" s="27"/>
     </row>
-    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="57"/>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="54"/>
       <c r="B71" s="1"/>
       <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
+      <c r="D71" s="34" t="s">
+        <v>31</v>
+      </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="45" t="s">
-        <v>107</v>
+      <c r="G71" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="H71" s="27"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="B72" s="14"/>
-      <c r="C72" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G72" s="14"/>
-      <c r="H72" s="15"/>
+      <c r="A72" s="54"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="34"/>
+      <c r="D72" s="34"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="H72" s="27"/>
     </row>
     <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="55"/>
-      <c r="B73" s="17"/>
-      <c r="C73" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D73" s="17"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G73" s="17"/>
-      <c r="H73" s="18"/>
+      <c r="A73" s="57"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="34"/>
+      <c r="D73" s="34"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="H73" s="27"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="B74" s="14"/>
+      <c r="C74" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G74" s="14"/>
+      <c r="H74" s="15"/>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="55"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D75" s="17"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" s="17"/>
+      <c r="H75" s="18"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="H76" s="15"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="54"/>
+      <c r="B77" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B74" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F74" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G74" s="14" t="s">
+      <c r="C77" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H74" s="15"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="54"/>
-      <c r="B75" s="1" t="s">
+      <c r="D77" s="1"/>
+      <c r="E77" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="G77" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H75" s="19"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="54"/>
-      <c r="B76" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H76" s="19"/>
-    </row>
-    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="55"/>
-      <c r="B77" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="17"/>
-      <c r="G77" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H77" s="18"/>
+      <c r="H77" s="19"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="58" t="s">
-        <v>117</v>
-      </c>
-      <c r="B78" s="34" t="s">
-        <v>28</v>
+      <c r="A78" s="54"/>
+      <c r="B78" s="31" t="s">
+        <v>71</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="1" t="s">
+      <c r="G78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H78" s="19"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="54"/>
-      <c r="B79" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H79" s="19"/>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="55"/>
+      <c r="B79" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="17"/>
+      <c r="G79" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="H79" s="18"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="54"/>
-      <c r="B80" s="34"/>
+      <c r="A80" s="58" t="s">
+        <v>115</v>
+      </c>
+      <c r="B80" s="34" t="s">
+        <v>28</v>
+      </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="44" t="s">
-        <v>43</v>
+      <c r="G80" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="H80" s="19"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="54"/>
-      <c r="B81" s="34"/>
+      <c r="B81" s="34" t="s">
+        <v>83</v>
+      </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="45" t="s">
-        <v>91</v>
+      <c r="G81" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="H81" s="19"/>
     </row>
@@ -6929,179 +6976,203 @@
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="2" t="s">
+      <c r="G82" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="H82" s="19"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="54"/>
+      <c r="B83" s="34"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="H83" s="19"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="54"/>
+      <c r="B84" s="34"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H82" s="19"/>
-    </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="55"/>
-      <c r="B83" s="36"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="17"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="17"/>
-      <c r="G83" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="H83" s="18"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="15"/>
+      <c r="H84" s="19"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="55"/>
-      <c r="B85" s="17"/>
+      <c r="B85" s="36"/>
       <c r="C85" s="17"/>
-      <c r="D85" s="23" t="s">
-        <v>121</v>
-      </c>
+      <c r="D85" s="17"/>
       <c r="E85" s="17"/>
       <c r="F85" s="17"/>
-      <c r="G85" s="17"/>
+      <c r="G85" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="H85" s="18"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="53" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
-      <c r="D86" s="14"/>
+      <c r="D86" s="22" t="s">
+        <v>12</v>
+      </c>
       <c r="E86" s="14"/>
       <c r="F86" s="14"/>
-      <c r="G86" s="22" t="s">
+      <c r="G86" s="14"/>
+      <c r="H86" s="15"/>
+    </row>
+    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="55"/>
+      <c r="B87" s="17"/>
+      <c r="C87" s="17"/>
+      <c r="D87" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E87" s="17"/>
+      <c r="F87" s="17"/>
+      <c r="G87" s="17"/>
+      <c r="H87" s="18"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H86" s="15"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="54"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="25" t="s">
+      <c r="H88" s="15"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="54"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H87" s="19"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="54"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="26" t="s">
+      <c r="H89" s="19"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="54"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="H88" s="19"/>
-    </row>
-    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="55"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
-      <c r="D89" s="17"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="17"/>
-      <c r="G89" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="H89" s="18"/>
-    </row>
-    <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="B90" s="50"/>
-      <c r="C90" s="51"/>
-      <c r="D90" s="51"/>
-      <c r="E90" s="51"/>
-      <c r="F90" s="51"/>
-      <c r="G90" s="51"/>
-      <c r="H90" s="52"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="B91" s="14"/>
-      <c r="C91" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E91" s="14"/>
-      <c r="F91" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="G91" s="14"/>
-      <c r="H91" s="15"/>
+      <c r="H90" s="19"/>
+    </row>
+    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="55"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="17"/>
+      <c r="E91" s="17"/>
+      <c r="F91" s="17"/>
+      <c r="G91" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="H91" s="18"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="55"/>
-      <c r="B92" s="17"/>
-      <c r="C92" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D92" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E92" s="17"/>
-      <c r="F92" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="G92" s="17"/>
-      <c r="H92" s="18"/>
+      <c r="A92" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B92" s="50"/>
+      <c r="C92" s="51"/>
+      <c r="D92" s="51"/>
+      <c r="E92" s="51"/>
+      <c r="F92" s="51"/>
+      <c r="G92" s="51"/>
+      <c r="H92" s="52"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="53" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B93" s="14"/>
-      <c r="C93" s="14"/>
-      <c r="D93" s="22" t="s">
-        <v>12</v>
+      <c r="C93" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="E93" s="14"/>
-      <c r="F93" s="14"/>
+      <c r="F93" s="28" t="s">
+        <v>29</v>
+      </c>
       <c r="G93" s="14"/>
       <c r="H93" s="15"/>
     </row>
     <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="55"/>
       <c r="B94" s="17"/>
-      <c r="C94" s="17"/>
-      <c r="D94" s="23" t="s">
-        <v>121</v>
+      <c r="C94" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D94" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="E94" s="17"/>
-      <c r="F94" s="17"/>
+      <c r="F94" s="30" t="s">
+        <v>124</v>
+      </c>
       <c r="G94" s="17"/>
       <c r="H94" s="18"/>
     </row>
-    <row r="95" spans="1:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="56"/>
-      <c r="C95" s="56"/>
-      <c r="D95" s="56"/>
-      <c r="E95" s="56"/>
-      <c r="F95" s="56"/>
-      <c r="G95" s="56"/>
-      <c r="H95" s="56"/>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="B95" s="14"/>
+      <c r="C95" s="14"/>
+      <c r="D95" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" s="14"/>
+      <c r="F95" s="14"/>
+      <c r="G95" s="14"/>
+      <c r="H95" s="15"/>
+    </row>
+    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="55"/>
+      <c r="B96" s="17"/>
+      <c r="C96" s="17"/>
+      <c r="D96" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E96" s="17"/>
+      <c r="F96" s="17"/>
+      <c r="G96" s="17"/>
+      <c r="H96" s="18"/>
+    </row>
+    <row r="97" spans="2:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="56"/>
+      <c r="C97" s="56"/>
+      <c r="D97" s="56"/>
+      <c r="E97" s="56"/>
+      <c r="F97" s="56"/>
+      <c r="G97" s="56"/>
+      <c r="H97" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -7112,29 +7183,29 @@
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A24:A35"/>
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="A91:A92"/>
     <mergeCell ref="A93:A94"/>
-    <mergeCell ref="B95:H95"/>
-    <mergeCell ref="A64:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B97:H97"/>
+    <mergeCell ref="A66:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="A80:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B48:H48"/>
     <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B63:H63"/>
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B92:H92"/>
+    <mergeCell ref="A88:A91"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A64"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A45"/>
+    <mergeCell ref="A46:A47"/>
     <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A55:A62"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A49:A50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="33" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -7154,7 +7225,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="60" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -7162,7 +7233,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="61" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C5" s="61"/>
       <c r="D5" s="61"/>
@@ -7173,16 +7244,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7323,7 +7394,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -7340,7 +7411,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -7357,7 +7428,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -7374,7 +7445,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -7391,7 +7462,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -7408,7 +7479,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -7425,7 +7496,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -7442,7 +7513,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -7459,7 +7530,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -7476,7 +7547,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -7493,7 +7564,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -7510,7 +7581,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -7527,7 +7598,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -7544,7 +7615,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -7561,7 +7632,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -7578,7 +7649,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -7595,7 +7666,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -7612,7 +7683,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -7629,7 +7700,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -7679,40 +7750,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S16.xlsx
+++ b/Plannings 2026 S16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7BDFEA3-BF96-4147-B5B1-379671B0AC15}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76BB87E3-F741-4956-A700-7D3CF6913999}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -471,10 +471,10 @@
     <t>15:45/17:30</t>
   </si>
   <si>
-    <t>17:30/20:30</t>
-  </si>
-  <si>
-    <t>18h45/20:30</t>
+    <t>18:30/20:30</t>
+  </si>
+  <si>
+    <t>17:30/18:30</t>
   </si>
 </sst>
 </file>
@@ -6238,7 +6238,7 @@
         <v>63</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E31" s="29"/>
       <c r="F31" s="1"/>
@@ -6264,7 +6264,7 @@
       <c r="B33" s="25"/>
       <c r="C33" s="39"/>
       <c r="D33" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E33" s="29"/>
       <c r="F33" s="1"/>

--- a/Plannings 2026 S16.xlsx
+++ b/Plannings 2026 S16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76BB87E3-F741-4956-A700-7D3CF6913999}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AC06566-40A6-48A4-B6BB-CE531FFC11A6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="152">
   <si>
     <t>Planning des salariés du 13/04/2026 au 19/04/2026</t>
   </si>
@@ -216,9 +216,6 @@
     <t>16:45/17:45</t>
   </si>
   <si>
-    <t>17:45/21:15</t>
-  </si>
-  <si>
     <t>DIVIEN Yohan</t>
   </si>
   <si>
@@ -475,6 +472,12 @@
   </si>
   <si>
     <t>17:30/18:30</t>
+  </si>
+  <si>
+    <t>18:15/19:15</t>
+  </si>
+  <si>
+    <t>19:15/21:15</t>
   </si>
 </sst>
 </file>
@@ -5354,6 +5357,94 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93185C26-956E-434F-9EFD-24B55172EF2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9756321" y="5769429"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B2C85A5-2BA7-488A-9CE3-6B31F0EF2282}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9756321" y="6150429"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5756,25 +5847,25 @@
     </row>
     <row r="3" spans="1:8" s="62" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3" s="63" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="63" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="63" t="s">
-        <v>147</v>
-      </c>
-      <c r="E3" s="63" t="s">
+      <c r="F3" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" s="63" t="s">
         <v>144</v>
       </c>
-      <c r="F3" s="63" t="s">
-        <v>142</v>
-      </c>
-      <c r="G3" s="63" t="s">
-        <v>145</v>
-      </c>
       <c r="H3" s="63" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6206,7 +6297,7 @@
         <v>61</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E29" s="29"/>
       <c r="F29" s="1"/>
@@ -6238,7 +6329,7 @@
         <v>63</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E31" s="29"/>
       <c r="F31" s="1"/>
@@ -6262,9 +6353,11 @@
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="57"/>
       <c r="B33" s="25"/>
-      <c r="C33" s="39"/>
+      <c r="C33" s="39" t="s">
+        <v>150</v>
+      </c>
       <c r="D33" s="25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E33" s="29"/>
       <c r="F33" s="1"/>
@@ -6274,7 +6367,9 @@
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="57"/>
       <c r="B34" s="25"/>
-      <c r="C34" s="39"/>
+      <c r="C34" s="26" t="s">
+        <v>49</v>
+      </c>
       <c r="D34" s="25"/>
       <c r="E34" s="29"/>
       <c r="F34" s="1"/>
@@ -6285,7 +6380,7 @@
       <c r="A35" s="55"/>
       <c r="B35" s="23"/>
       <c r="C35" s="23" t="s">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="D35" s="23"/>
       <c r="E35" s="30"/>
@@ -6295,7 +6390,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -6321,7 +6416,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B38" s="22" t="s">
         <v>12</v>
@@ -6338,7 +6433,7 @@
       </c>
       <c r="G38" s="14"/>
       <c r="H38" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -6348,27 +6443,27 @@
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="F39" s="25" t="s">
         <v>20</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="54"/>
       <c r="B40" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="2" t="s">
@@ -6376,13 +6471,13 @@
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="54"/>
       <c r="B41" s="29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="25" t="s">
@@ -6390,11 +6485,11 @@
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -6416,13 +6511,13 @@
       <c r="B43" s="29"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -6430,7 +6525,7 @@
       <c r="B44" s="29"/>
       <c r="C44" s="1"/>
       <c r="D44" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -6442,7 +6537,7 @@
       <c r="B45" s="30"/>
       <c r="C45" s="17"/>
       <c r="D45" s="23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="17"/>
@@ -6451,7 +6546,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="53" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -6469,7 +6564,7 @@
       <c r="C47" s="17"/>
       <c r="D47" s="17"/>
       <c r="E47" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F47" s="17"/>
       <c r="G47" s="17"/>
@@ -6477,7 +6572,7 @@
     </row>
     <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B48" s="50"/>
       <c r="C48" s="51"/>
@@ -6489,7 +6584,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -6510,12 +6605,12 @@
       <c r="F50" s="17"/>
       <c r="G50" s="17"/>
       <c r="H50" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="53" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B51" s="35" t="s">
         <v>28</v>
@@ -6534,13 +6629,13 @@
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="57"/>
       <c r="B52" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C52" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="C52" s="34" t="s">
-        <v>84</v>
-      </c>
       <c r="D52" s="34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -6549,7 +6644,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -6570,12 +6665,12 @@
       <c r="F54" s="17"/>
       <c r="G54" s="17"/>
       <c r="H54" s="41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="53" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -6601,7 +6696,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -6622,7 +6717,7 @@
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -6646,7 +6741,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -6670,7 +6765,7 @@
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -6694,12 +6789,12 @@
       <c r="F64" s="17"/>
       <c r="G64" s="17"/>
       <c r="H64" s="41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B65" s="50"/>
       <c r="C65" s="51"/>
@@ -6711,7 +6806,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>15</v>
@@ -6730,29 +6825,29 @@
         <v>12</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="54"/>
       <c r="B67" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C67" s="25" t="s">
         <v>20</v>
       </c>
       <c r="D67" s="25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="H67" s="27" t="s">
         <v>100</v>
-      </c>
-      <c r="H67" s="27" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -6767,7 +6862,7 @@
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H68" s="27"/>
     </row>
@@ -6775,15 +6870,15 @@
       <c r="A69" s="54"/>
       <c r="B69" s="1"/>
       <c r="C69" s="34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H69" s="27"/>
     </row>
@@ -6811,7 +6906,7 @@
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H71" s="27"/>
     </row>
@@ -6835,13 +6930,13 @@
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H73" s="27"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="53" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B74" s="14"/>
       <c r="C74" s="22" t="s">
@@ -6871,7 +6966,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B76" s="14" t="s">
         <v>15</v>
@@ -6887,34 +6982,34 @@
         <v>15</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H76" s="15"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="54"/>
       <c r="B77" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="D77" s="1"/>
       <c r="E77" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="G77" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="H77" s="19"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="54"/>
       <c r="B78" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -6928,20 +7023,20 @@
     <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="55"/>
       <c r="B79" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C79" s="17"/>
       <c r="D79" s="17"/>
       <c r="E79" s="17"/>
       <c r="F79" s="17"/>
       <c r="G79" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H79" s="18"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="58" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B80" s="34" t="s">
         <v>28</v>
@@ -6958,14 +7053,14 @@
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="54"/>
       <c r="B81" s="34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H81" s="19"/>
     </row>
@@ -6989,7 +7084,7 @@
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H83" s="19"/>
     </row>
@@ -7013,13 +7108,13 @@
       <c r="E85" s="17"/>
       <c r="F85" s="17"/>
       <c r="G85" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H85" s="18"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="53" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -7036,7 +7131,7 @@
       <c r="B87" s="17"/>
       <c r="C87" s="17"/>
       <c r="D87" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E87" s="17"/>
       <c r="F87" s="17"/>
@@ -7045,7 +7140,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="53" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -7089,13 +7184,13 @@
       <c r="E91" s="17"/>
       <c r="F91" s="17"/>
       <c r="G91" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H91" s="18"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B92" s="50"/>
       <c r="C92" s="51"/>
@@ -7107,7 +7202,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="53" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B93" s="14"/>
       <c r="C93" s="14" t="s">
@@ -7127,21 +7222,21 @@
       <c r="A94" s="55"/>
       <c r="B94" s="17"/>
       <c r="C94" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D94" s="17" t="s">
         <v>16</v>
       </c>
       <c r="E94" s="17"/>
       <c r="F94" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G94" s="17"/>
       <c r="H94" s="18"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="53" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
@@ -7158,7 +7253,7 @@
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
       <c r="D96" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E96" s="17"/>
       <c r="F96" s="17"/>
@@ -7225,7 +7320,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="60" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -7233,7 +7328,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5" s="61"/>
       <c r="D5" s="61"/>
@@ -7244,16 +7339,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7394,7 +7489,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -7411,7 +7506,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -7428,7 +7523,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -7445,7 +7540,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -7462,7 +7557,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -7479,7 +7574,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -7496,7 +7591,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -7513,7 +7608,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -7530,7 +7625,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -7547,7 +7642,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -7564,7 +7659,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -7581,7 +7676,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -7598,7 +7693,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -7615,7 +7710,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -7632,7 +7727,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -7649,7 +7744,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -7666,7 +7761,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -7683,7 +7778,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -7700,7 +7795,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -7750,40 +7845,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>136</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S16.xlsx
+++ b/Plannings 2026 S16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AC06566-40A6-48A4-B6BB-CE531FFC11A6}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FD16D83-841A-4024-ABAE-EB41FA720CC5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="150">
   <si>
     <t>Planning des salariés du 13/04/2026 au 19/04/2026</t>
   </si>
@@ -210,12 +210,21 @@
     <t>14:15/16:45</t>
   </si>
   <si>
+    <t>15:45/17:00</t>
+  </si>
+  <si>
     <t>18:00/21:15</t>
   </si>
   <si>
     <t>16:45/17:45</t>
   </si>
   <si>
+    <t>17:00/20:30</t>
+  </si>
+  <si>
+    <t>17:45/21:15</t>
+  </si>
+  <si>
     <t>DIVIEN Yohan</t>
   </si>
   <si>
@@ -463,21 +472,6 @@
   </si>
   <si>
     <t>C. PADEL // EDF // LEAGUES // LDC : BAYERN-REAL // TOURNOI IGENSIA</t>
-  </si>
-  <si>
-    <t>15:45/17:30</t>
-  </si>
-  <si>
-    <t>18:30/20:30</t>
-  </si>
-  <si>
-    <t>17:30/18:30</t>
-  </si>
-  <si>
-    <t>18:15/19:15</t>
-  </si>
-  <si>
-    <t>19:15/21:15</t>
   </si>
 </sst>
 </file>
@@ -2809,21 +2803,1385 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2851,23 +4209,507 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2895,23 +4737,551 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB3C0959-561A-424C-8F34-0D5E0F21F5E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8041821" y="979714"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88CA5A6A-9453-477E-895D-3F528B2093C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2927,2515 +5297,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB3C0959-561A-424C-8F34-0D5E0F21F5E3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8041821" y="979714"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88CA5A6A-9453-477E-895D-3F528B2093C6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
           <a:off x="10722429" y="1755321"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBBB8A6D-5DB9-4041-BF37-9B1BE859B8DA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3252107" y="5769429"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93185C26-956E-434F-9EFD-24B55172EF2B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9756321" y="5769429"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="41" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B2C85A5-2BA7-488A-9CE3-6B31F0EF2282}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9756321" y="6150429"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5817,7 +5679,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="48.7109375" customWidth="1"/>
@@ -5847,25 +5709,25 @@
     </row>
     <row r="3" spans="1:8" s="62" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D3" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="63" t="s">
         <v>146</v>
       </c>
-      <c r="E3" s="63" t="s">
+      <c r="F3" s="63" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" s="63" t="s">
+        <v>147</v>
+      </c>
+      <c r="H3" s="63" t="s">
         <v>143</v>
-      </c>
-      <c r="F3" s="63" t="s">
-        <v>141</v>
-      </c>
-      <c r="G3" s="63" t="s">
-        <v>144</v>
-      </c>
-      <c r="H3" s="63" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6297,7 +6159,7 @@
         <v>61</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>147</v>
+        <v>62</v>
       </c>
       <c r="E29" s="29"/>
       <c r="F29" s="1"/>
@@ -6323,13 +6185,13 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="54"/>
       <c r="B31" s="25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>149</v>
+        <v>65</v>
       </c>
       <c r="E31" s="29"/>
       <c r="F31" s="1"/>
@@ -6342,319 +6204,317 @@
       <c r="C32" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="D32" s="26" t="s">
-        <v>49</v>
-      </c>
+      <c r="D32" s="25"/>
       <c r="E32" s="29"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="19"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="57"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="E33" s="29"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="19"/>
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="55"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="23"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="18"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="57"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="19"/>
+      <c r="A34" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" s="15"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="55"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="D35" s="23"/>
-      <c r="E35" s="30"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
       <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
+      <c r="G35" s="23" t="s">
+        <v>13</v>
+      </c>
       <c r="H35" s="18"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="14"/>
+        <v>68</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>12</v>
+      </c>
       <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="22" t="s">
+      <c r="D36" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H36" s="15"/>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="55"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H37" s="18"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="54"/>
+      <c r="B37" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="27" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="B38" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14" t="s">
+      <c r="A38" s="54"/>
+      <c r="B38" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E38" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" s="14"/>
-      <c r="H38" s="24" t="s">
-        <v>66</v>
+      <c r="G38" s="1"/>
+      <c r="H38" s="42" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="54"/>
-      <c r="B39" s="25" t="s">
-        <v>20</v>
+      <c r="B39" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F39" s="25" t="s">
-        <v>20</v>
+      <c r="D39" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="H39" s="27" t="s">
-        <v>69</v>
+      <c r="H39" s="43" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="54"/>
-      <c r="B40" s="31" t="s">
-        <v>70</v>
-      </c>
+      <c r="B40" s="29"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="26" t="s">
-        <v>71</v>
+      <c r="D40" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E40" s="1"/>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="21" t="s">
         <v>15</v>
-      </c>
-      <c r="G40" s="1"/>
-      <c r="H40" s="42" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="54"/>
-      <c r="B41" s="29" t="s">
-        <v>73</v>
-      </c>
+      <c r="B41" s="29"/>
       <c r="C41" s="1"/>
-      <c r="D41" s="25" t="s">
-        <v>58</v>
+      <c r="D41" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="E41" s="1"/>
-      <c r="F41" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="43" t="s">
-        <v>75</v>
+      <c r="H41" s="19" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="54"/>
       <c r="B42" s="29"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="2" t="s">
-        <v>15</v>
+      <c r="D42" s="26" t="s">
+        <v>74</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="21" t="s">
+      <c r="H42" s="19"/>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="55"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="18"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="54"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="54"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="19"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="15"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="55"/>
-      <c r="B45" s="30"/>
+      <c r="B45" s="17"/>
       <c r="C45" s="17"/>
-      <c r="D45" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17" t="s">
+        <v>83</v>
+      </c>
       <c r="F45" s="17"/>
       <c r="G45" s="17"/>
       <c r="H45" s="18"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14" t="s">
+    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" s="50"/>
+      <c r="C46" s="51"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="52"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="15"/>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="55"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B48" s="50"/>
-      <c r="C48" s="51"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="51"/>
-      <c r="F48" s="51"/>
-      <c r="G48" s="51"/>
-      <c r="H48" s="52"/>
+      <c r="A48" s="55"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="18" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
+        <v>142</v>
+      </c>
+      <c r="B49" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="35" t="s">
+        <v>28</v>
+      </c>
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
       <c r="G49" s="14"/>
-      <c r="H49" s="15" t="s">
-        <v>15</v>
-      </c>
+      <c r="H49" s="15"/>
     </row>
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="55"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="18" t="s">
+      <c r="A50" s="57"/>
+      <c r="B50" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" s="34" t="s">
         <v>86</v>
       </c>
+      <c r="D50" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="19"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="B51" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="C51" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="D51" s="35" t="s">
-        <v>28</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
       <c r="G51" s="14"/>
-      <c r="H51" s="15"/>
+      <c r="H51" s="40" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="57"/>
-      <c r="B52" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C52" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="D52" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="19"/>
+      <c r="A52" s="55"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="41" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="53" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
+      <c r="F53" s="22" t="s">
+        <v>12</v>
+      </c>
       <c r="G53" s="14"/>
-      <c r="H53" s="40" t="s">
-        <v>43</v>
-      </c>
+      <c r="H53" s="15"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="55"/>
@@ -6662,50 +6522,48 @@
       <c r="C54" s="17"/>
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
+      <c r="F54" s="23" t="s">
+        <v>20</v>
+      </c>
       <c r="G54" s="17"/>
-      <c r="H54" s="41" t="s">
-        <v>88</v>
-      </c>
+      <c r="H54" s="18"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="53" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="22" t="s">
-        <v>12</v>
-      </c>
+      <c r="F55" s="14"/>
       <c r="G55" s="14"/>
-      <c r="H55" s="15"/>
-    </row>
-    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="55"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" s="17"/>
-      <c r="H56" s="18"/>
+      <c r="H55" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="54"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="19" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="15" t="s">
-        <v>15</v>
+      <c r="A57" s="54"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="42" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -6716,8 +6574,8 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
-      <c r="H58" s="19" t="s">
-        <v>91</v>
+      <c r="H58" s="43" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -6728,8 +6586,8 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
-      <c r="H59" s="42" t="s">
-        <v>43</v>
+      <c r="H59" s="21" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -6740,8 +6598,8 @@
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="43" t="s">
-        <v>92</v>
+      <c r="H60" s="19" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -6752,133 +6610,137 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="21" t="s">
+      <c r="H61" s="42" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="55"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="41" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B63" s="50"/>
+      <c r="C63" s="51"/>
+      <c r="D63" s="51"/>
+      <c r="E63" s="51"/>
+      <c r="F63" s="51"/>
+      <c r="G63" s="51"/>
+      <c r="H63" s="52"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" s="14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="54"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="19" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="54"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="42" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="55"/>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="41" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="B65" s="50"/>
-      <c r="C65" s="51"/>
-      <c r="D65" s="51"/>
-      <c r="E65" s="51"/>
-      <c r="F65" s="51"/>
-      <c r="G65" s="51"/>
-      <c r="H65" s="52"/>
+      <c r="C64" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" s="14"/>
+      <c r="G64" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H64" s="24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="54"/>
+      <c r="B65" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F65" s="1"/>
+      <c r="G65" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="H65" s="27" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="53" t="s">
-        <v>96</v>
-      </c>
-      <c r="B66" s="14" t="s">
+      <c r="A66" s="54"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D66" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F66" s="14"/>
-      <c r="G66" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H66" s="24" t="s">
-        <v>66</v>
-      </c>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="H66" s="27"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="54"/>
-      <c r="B67" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C67" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="D67" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="B67" s="1"/>
+      <c r="C67" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="H67" s="27" t="s">
-        <v>100</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="H67" s="27"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="54"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="33" t="s">
+      <c r="C68" s="34"/>
+      <c r="D68" s="33" t="s">
         <v>28</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="26" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="H68" s="27"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="54"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>101</v>
+      <c r="C69" s="34"/>
+      <c r="D69" s="34" t="s">
+        <v>31</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H69" s="27"/>
     </row>
@@ -6886,181 +6748,177 @@
       <c r="A70" s="54"/>
       <c r="B70" s="1"/>
       <c r="C70" s="34"/>
-      <c r="D70" s="33" t="s">
-        <v>28</v>
-      </c>
+      <c r="D70" s="34"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="26" t="s">
-        <v>12</v>
+      <c r="G70" s="44" t="s">
+        <v>43</v>
       </c>
       <c r="H70" s="27"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="54"/>
+    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="57"/>
       <c r="B71" s="1"/>
       <c r="C71" s="34"/>
-      <c r="D71" s="34" t="s">
-        <v>31</v>
-      </c>
+      <c r="D71" s="34"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="25" t="s">
-        <v>103</v>
+      <c r="G71" s="45" t="s">
+        <v>107</v>
       </c>
       <c r="H71" s="27"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="54"/>
-      <c r="B72" s="1"/>
-      <c r="C72" s="34"/>
-      <c r="D72" s="34"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="H72" s="27"/>
+      <c r="A72" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="B72" s="14"/>
+      <c r="C72" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G72" s="14"/>
+      <c r="H72" s="15"/>
     </row>
     <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="57"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="34"/>
-      <c r="D73" s="34"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="H73" s="27"/>
+      <c r="A73" s="55"/>
+      <c r="B73" s="17"/>
+      <c r="C73" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" s="17"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G73" s="17"/>
+      <c r="H73" s="18"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="B74" s="14"/>
-      <c r="C74" s="22" t="s">
-        <v>12</v>
+        <v>109</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G74" s="14"/>
+      <c r="E74" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>110</v>
+      </c>
       <c r="H74" s="15"/>
     </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="55"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D75" s="17"/>
-      <c r="E75" s="17"/>
-      <c r="F75" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G75" s="17"/>
-      <c r="H75" s="18"/>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="54"/>
+      <c r="B75" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H75" s="19"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="B76" s="14" t="s">
+      <c r="A76" s="54"/>
+      <c r="B76" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C76" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F76" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G76" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="H76" s="15"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="54"/>
-      <c r="B77" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H77" s="19"/>
+      <c r="H76" s="19"/>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="55"/>
+      <c r="B77" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="H77" s="18"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="54"/>
-      <c r="B78" s="31" t="s">
-        <v>70</v>
+      <c r="A78" s="58" t="s">
+        <v>117</v>
+      </c>
+      <c r="B78" s="34" t="s">
+        <v>28</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="2" t="s">
+      <c r="G78" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H78" s="19"/>
     </row>
-    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="55"/>
-      <c r="B79" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="C79" s="17"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="17"/>
-      <c r="G79" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="H79" s="18"/>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="54"/>
+      <c r="B79" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H79" s="19"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="58" t="s">
-        <v>114</v>
-      </c>
-      <c r="B80" s="34" t="s">
-        <v>28</v>
-      </c>
+      <c r="A80" s="54"/>
+      <c r="B80" s="34"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="1" t="s">
-        <v>15</v>
+      <c r="G80" s="44" t="s">
+        <v>43</v>
       </c>
       <c r="H80" s="19"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="54"/>
-      <c r="B81" s="34" t="s">
-        <v>82</v>
-      </c>
+      <c r="B81" s="34"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="1" t="s">
-        <v>115</v>
+      <c r="G81" s="45" t="s">
+        <v>91</v>
       </c>
       <c r="H81" s="19"/>
     </row>
@@ -7071,203 +6929,179 @@
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="44" t="s">
-        <v>43</v>
+      <c r="G82" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="H82" s="19"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="54"/>
-      <c r="B83" s="34"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="H83" s="19"/>
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="55"/>
+      <c r="B83" s="36"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="17"/>
+      <c r="G83" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="H83" s="18"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="54"/>
-      <c r="B84" s="34"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H84" s="19"/>
+      <c r="A84" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="B84" s="14"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="15"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="55"/>
-      <c r="B85" s="36"/>
+      <c r="B85" s="17"/>
       <c r="C85" s="17"/>
-      <c r="D85" s="17"/>
+      <c r="D85" s="23" t="s">
+        <v>121</v>
+      </c>
       <c r="E85" s="17"/>
       <c r="F85" s="17"/>
-      <c r="G85" s="17" t="s">
-        <v>116</v>
-      </c>
+      <c r="G85" s="17"/>
       <c r="H85" s="18"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="53" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
-      <c r="D86" s="22" t="s">
-        <v>12</v>
-      </c>
+      <c r="D86" s="14"/>
       <c r="E86" s="14"/>
       <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
+      <c r="G86" s="22" t="s">
+        <v>12</v>
+      </c>
       <c r="H86" s="15"/>
     </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="55"/>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E87" s="17"/>
-      <c r="F87" s="17"/>
-      <c r="G87" s="17"/>
-      <c r="H87" s="18"/>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="54"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H87" s="19"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="B88" s="14"/>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="22" t="s">
+      <c r="A88" s="54"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="H88" s="15"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="54"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="H89" s="19"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="54"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="H90" s="19"/>
-    </row>
-    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="55"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="17"/>
-      <c r="D91" s="17"/>
-      <c r="E91" s="17"/>
-      <c r="F91" s="17"/>
-      <c r="G91" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="H91" s="18"/>
+      <c r="H88" s="19"/>
+    </row>
+    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="55"/>
+      <c r="B89" s="17"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="17"/>
+      <c r="E89" s="17"/>
+      <c r="F89" s="17"/>
+      <c r="G89" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="H89" s="18"/>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B90" s="50"/>
+      <c r="C90" s="51"/>
+      <c r="D90" s="51"/>
+      <c r="E90" s="51"/>
+      <c r="F90" s="51"/>
+      <c r="G90" s="51"/>
+      <c r="H90" s="52"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B91" s="14"/>
+      <c r="C91" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E91" s="14"/>
+      <c r="F91" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="G91" s="14"/>
+      <c r="H91" s="15"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="B92" s="50"/>
-      <c r="C92" s="51"/>
-      <c r="D92" s="51"/>
-      <c r="E92" s="51"/>
-      <c r="F92" s="51"/>
-      <c r="G92" s="51"/>
-      <c r="H92" s="52"/>
+      <c r="A92" s="55"/>
+      <c r="B92" s="17"/>
+      <c r="C92" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D92" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E92" s="17"/>
+      <c r="F92" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="G92" s="17"/>
+      <c r="H92" s="18"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="53" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B93" s="14"/>
-      <c r="C93" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D93" s="14" t="s">
-        <v>15</v>
+      <c r="C93" s="14"/>
+      <c r="D93" s="22" t="s">
+        <v>12</v>
       </c>
       <c r="E93" s="14"/>
-      <c r="F93" s="28" t="s">
-        <v>29</v>
-      </c>
+      <c r="F93" s="14"/>
       <c r="G93" s="14"/>
       <c r="H93" s="15"/>
     </row>
     <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="55"/>
       <c r="B94" s="17"/>
-      <c r="C94" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="D94" s="17" t="s">
-        <v>16</v>
+      <c r="C94" s="17"/>
+      <c r="D94" s="23" t="s">
+        <v>121</v>
       </c>
       <c r="E94" s="17"/>
-      <c r="F94" s="30" t="s">
-        <v>123</v>
-      </c>
+      <c r="F94" s="17"/>
       <c r="G94" s="17"/>
       <c r="H94" s="18"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="B95" s="14"/>
-      <c r="C95" s="14"/>
-      <c r="D95" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E95" s="14"/>
-      <c r="F95" s="14"/>
-      <c r="G95" s="14"/>
-      <c r="H95" s="15"/>
-    </row>
-    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="55"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="17"/>
-      <c r="D96" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E96" s="17"/>
-      <c r="F96" s="17"/>
-      <c r="G96" s="17"/>
-      <c r="H96" s="18"/>
-    </row>
-    <row r="97" spans="2:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="56"/>
-      <c r="C97" s="56"/>
-      <c r="D97" s="56"/>
-      <c r="E97" s="56"/>
-      <c r="F97" s="56"/>
-      <c r="G97" s="56"/>
-      <c r="H97" s="56"/>
+    <row r="95" spans="1:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="56"/>
+      <c r="C95" s="56"/>
+      <c r="D95" s="56"/>
+      <c r="E95" s="56"/>
+      <c r="F95" s="56"/>
+      <c r="G95" s="56"/>
+      <c r="H95" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -7278,29 +7112,29 @@
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A35"/>
+    <mergeCell ref="A24:A33"/>
     <mergeCell ref="B2:H2"/>
+    <mergeCell ref="A91:A92"/>
     <mergeCell ref="A93:A94"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B97:H97"/>
-    <mergeCell ref="A66:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A79"/>
-    <mergeCell ref="A80:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="B95:H95"/>
+    <mergeCell ref="A64:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B46:H46"/>
     <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B65:H65"/>
-    <mergeCell ref="B92:H92"/>
-    <mergeCell ref="A88:A91"/>
+    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A62"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A43"/>
+    <mergeCell ref="A44:A45"/>
     <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A64"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A51:A52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="33" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -7320,7 +7154,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="60" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -7328,7 +7162,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="61" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C5" s="61"/>
       <c r="D5" s="61"/>
@@ -7339,16 +7173,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7489,7 +7323,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -7506,7 +7340,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -7523,7 +7357,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -7540,7 +7374,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -7557,7 +7391,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -7574,7 +7408,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -7591,7 +7425,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -7608,7 +7442,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -7625,7 +7459,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -7642,7 +7476,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -7659,7 +7493,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -7676,7 +7510,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -7693,7 +7527,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -7710,7 +7544,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -7727,7 +7561,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -7744,7 +7578,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -7761,7 +7595,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -7778,7 +7612,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -7795,7 +7629,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -7845,40 +7679,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S16.xlsx
+++ b/Plannings 2026 S16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA0D7B55-5008-461D-91AD-95FB1EABCD73}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9900B642-342D-450E-A203-5359A3871E24}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -435,9 +435,6 @@
     <t>LOUIBA Yacine</t>
   </si>
   <si>
-    <t>P50M // ANIV</t>
-  </si>
-  <si>
     <t>C. PADEL // EDF // CUP PADEL</t>
   </si>
   <si>
@@ -484,6 +481,9 @@
   </si>
   <si>
     <t>21:00/22:00</t>
+  </si>
+  <si>
+    <t>TRAINING CUP // P50M // ANIV</t>
   </si>
 </sst>
 </file>
@@ -5941,25 +5941,25 @@
     </row>
     <row r="3" spans="1:8" s="62" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="63" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="63" t="s">
-        <v>142</v>
-      </c>
-      <c r="D3" s="63" t="s">
-        <v>143</v>
-      </c>
-      <c r="E3" s="63" t="s">
+      <c r="F3" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="F3" s="63" t="s">
-        <v>138</v>
-      </c>
-      <c r="G3" s="63" t="s">
-        <v>141</v>
-      </c>
       <c r="H3" s="63" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6063,7 +6063,7 @@
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="54"/>
       <c r="B10" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -6099,7 +6099,7 @@
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="54"/>
       <c r="B12" s="34" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C12" s="34" t="s">
         <v>23</v>
@@ -6133,7 +6133,7 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="57"/>
       <c r="B14" s="34" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C14" s="34" t="s">
         <v>29</v>
@@ -6237,10 +6237,10 @@
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="55"/>
       <c r="B21" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>149</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>150</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>36</v>
@@ -6415,7 +6415,7 @@
         <v>58</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E31" s="29"/>
       <c r="F31" s="1"/>
@@ -6447,7 +6447,7 @@
         <v>60</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" s="29"/>
       <c r="F33" s="1"/>
@@ -6472,10 +6472,10 @@
       <c r="A35" s="57"/>
       <c r="B35" s="25"/>
       <c r="C35" s="39" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E35" s="29"/>
       <c r="F35" s="1"/>
@@ -6498,7 +6498,7 @@
       <c r="A37" s="55"/>
       <c r="B37" s="23"/>
       <c r="C37" s="23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D37" s="23"/>
       <c r="E37" s="30"/>

--- a/Plannings 2026 S16.xlsx
+++ b/Plannings 2026 S16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9900B642-342D-450E-A203-5359A3871E24}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5562AB7D-C39E-413F-90FA-D51330391F8C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="153">
   <si>
     <t>Planning des salariés du 13/04/2026 au 19/04/2026</t>
   </si>
@@ -120,9 +120,6 @@
     <t>CASTELLON Pascaline</t>
   </si>
   <si>
-    <t>17:30/22:00</t>
-  </si>
-  <si>
     <t>07:30/13:00</t>
   </si>
   <si>
@@ -447,12 +444,6 @@
     <t>EDF // ANIV</t>
   </si>
   <si>
-    <t>C. PADEL // EDF // LEAGUES // LDC : LIVERPOOL-PSG</t>
-  </si>
-  <si>
-    <t>C. PADEL // EDF // LEAGUES // LDC : BAYERN-REAL // TOURNOI IGENSIA</t>
-  </si>
-  <si>
     <t>15:45/17:30</t>
   </si>
   <si>
@@ -484,6 +475,12 @@
   </si>
   <si>
     <t>TRAINING CUP // P50M // ANIV</t>
+  </si>
+  <si>
+    <t>C. PADEL     //     EDF     //     LEAGUES     //     LDC : LIVERPOOL-PSG</t>
+  </si>
+  <si>
+    <t>C. PADEL     //     EDF     //     LEAGUES      //      LDC : BAYERN-REAL // TOURNOI IGENSIA</t>
   </si>
 </sst>
 </file>
@@ -493,7 +490,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -582,6 +579,12 @@
     <font>
       <sz val="8"/>
       <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -879,7 +882,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1070,6 +1073,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1669,23 +1675,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1713,23 +1807,903 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="42" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1757,23 +2731,199 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1801,23 +2951,595 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1845,23 +3567,463 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1889,23 +4051,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1933,23 +4139,331 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1977,23 +4491,1035 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB3C0959-561A-424C-8F34-0D5E0F21F5E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8041821" y="979714"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88CA5A6A-9453-477E-895D-3F528B2093C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10722429" y="1755321"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBBB8A6D-5DB9-4041-BF37-9B1BE859B8DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3252107" y="5769429"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93185C26-956E-434F-9EFD-24B55172EF2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9756321" y="5769429"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B2C85A5-2BA7-488A-9CE3-6B31F0EF2282}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9756321" y="6150429"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CBF850C-75C9-4F55-9044-9172EF900B3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16260536" y="8082643"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A6081C7-6C02-46EE-8A63-9B566B769A1E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6504214" y="2462893"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA8A7C46-B970-4262-B903-E62E3CBFEB5C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2009,3527 +5535,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB3C0959-561A-424C-8F34-0D5E0F21F5E3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8041821" y="979714"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88CA5A6A-9453-477E-895D-3F528B2093C6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10722429" y="1755321"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBBB8A6D-5DB9-4041-BF37-9B1BE859B8DA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3252107" y="5769429"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93185C26-956E-434F-9EFD-24B55172EF2B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9756321" y="5769429"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="41" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B2C85A5-2BA7-488A-9CE3-6B31F0EF2282}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9756321" y="6150429"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CBF850C-75C9-4F55-9044-9172EF900B3F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16260536" y="8082643"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A6081C7-6C02-46EE-8A63-9B566B769A1E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6504214" y="2462893"/>
+          <a:off x="6504214" y="3238500"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5914,7 +5920,7 @@
   <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="48.7109375" customWidth="1"/>
+    <col min="1" max="8" width="52" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5941,25 +5947,25 @@
     </row>
     <row r="3" spans="1:8" s="62" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="63" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="63" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" s="63" t="s">
-        <v>142</v>
-      </c>
-      <c r="E3" s="63" t="s">
+      <c r="F3" s="63" t="s">
+        <v>136</v>
+      </c>
+      <c r="G3" s="63" t="s">
         <v>139</v>
       </c>
-      <c r="F3" s="63" t="s">
-        <v>137</v>
-      </c>
-      <c r="G3" s="63" t="s">
-        <v>140</v>
-      </c>
       <c r="H3" s="63" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6063,7 +6069,7 @@
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="54"/>
       <c r="B10" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -6099,7 +6105,7 @@
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="54"/>
       <c r="B12" s="34" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C12" s="34" t="s">
         <v>23</v>
@@ -6133,7 +6139,7 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="57"/>
       <c r="B14" s="34" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C14" s="34" t="s">
         <v>29</v>
@@ -6175,9 +6181,7 @@
         <v>31</v>
       </c>
       <c r="B17" s="14"/>
-      <c r="C17" s="14" t="s">
-        <v>15</v>
-      </c>
+      <c r="C17" s="14"/>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="14"/>
@@ -6189,20 +6193,18 @@
     <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="55"/>
       <c r="B18" s="17"/>
-      <c r="C18" s="17" t="s">
-        <v>32</v>
-      </c>
+      <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
       <c r="H18" s="49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="50"/>
       <c r="C19" s="51"/>
@@ -6214,7 +6216,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="53" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>15</v>
@@ -6237,29 +6239,31 @@
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="55"/>
       <c r="B21" s="17" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D21" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="F21" s="17" t="s">
         <v>37</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>38</v>
       </c>
       <c r="G21" s="17"/>
       <c r="H21" s="18"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
+      <c r="C22" s="14" t="s">
+        <v>15</v>
+      </c>
       <c r="D22" s="14" t="s">
         <v>15</v>
       </c>
@@ -6268,23 +6272,25 @@
         <v>15</v>
       </c>
       <c r="G22" s="46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H22" s="15"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="54"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
+      <c r="C23" s="64" t="s">
+        <v>93</v>
+      </c>
       <c r="D23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" s="45" t="s">
         <v>42</v>
-      </c>
-      <c r="G23" s="45" t="s">
-        <v>43</v>
       </c>
       <c r="H23" s="19"/>
     </row>
@@ -6308,22 +6314,22 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H25" s="19"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="38" t="s">
-        <v>46</v>
-      </c>
       <c r="C26" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26" s="28" t="s">
         <v>22</v>
@@ -6337,13 +6343,13 @@
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="54"/>
       <c r="B27" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="D27" s="25" t="s">
         <v>48</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>49</v>
       </c>
       <c r="E27" s="29" t="s">
         <v>25</v>
@@ -6351,19 +6357,19 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="54"/>
       <c r="B28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D28" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" s="29"/>
       <c r="F28" s="1"/>
@@ -6375,19 +6381,19 @@
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="54"/>
       <c r="B29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="E29" s="29"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -6396,10 +6402,10 @@
         <v>27</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E30" s="29"/>
       <c r="F30" s="1"/>
@@ -6409,13 +6415,13 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="54"/>
       <c r="B31" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="39" t="s">
-        <v>58</v>
-      </c>
       <c r="D31" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E31" s="29"/>
       <c r="F31" s="1"/>
@@ -6425,13 +6431,13 @@
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="54"/>
       <c r="B32" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" s="29"/>
       <c r="F32" s="1"/>
@@ -6441,13 +6447,13 @@
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="54"/>
       <c r="B33" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="D33" s="39" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E33" s="29"/>
       <c r="F33" s="1"/>
@@ -6458,10 +6464,10 @@
       <c r="A34" s="54"/>
       <c r="B34" s="25"/>
       <c r="C34" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E34" s="29"/>
       <c r="F34" s="1"/>
@@ -6472,10 +6478,10 @@
       <c r="A35" s="57"/>
       <c r="B35" s="25"/>
       <c r="C35" s="39" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E35" s="29"/>
       <c r="F35" s="1"/>
@@ -6486,7 +6492,7 @@
       <c r="A36" s="57"/>
       <c r="B36" s="25"/>
       <c r="C36" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="29"/>
@@ -6498,7 +6504,7 @@
       <c r="A37" s="55"/>
       <c r="B37" s="23"/>
       <c r="C37" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D37" s="23"/>
       <c r="E37" s="30"/>
@@ -6508,7 +6514,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -6534,7 +6540,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B40" s="22" t="s">
         <v>12</v>
@@ -6551,7 +6557,7 @@
       </c>
       <c r="G40" s="14"/>
       <c r="H40" s="24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -6561,27 +6567,27 @@
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="F41" s="25" t="s">
         <v>19</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="54"/>
       <c r="B42" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="2" t="s">
@@ -6589,25 +6595,25 @@
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="54"/>
       <c r="B43" s="29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -6629,13 +6635,13 @@
       <c r="B45" s="29"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -6643,7 +6649,7 @@
       <c r="B46" s="29"/>
       <c r="C46" s="1"/>
       <c r="D46" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -6655,7 +6661,7 @@
       <c r="B47" s="30"/>
       <c r="C47" s="17"/>
       <c r="D47" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E47" s="17"/>
       <c r="F47" s="17"/>
@@ -6664,7 +6670,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -6682,7 +6688,7 @@
       <c r="C49" s="17"/>
       <c r="D49" s="17"/>
       <c r="E49" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F49" s="17"/>
       <c r="G49" s="17"/>
@@ -6690,7 +6696,7 @@
     </row>
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B50" s="50"/>
       <c r="C50" s="51"/>
@@ -6702,7 +6708,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -6723,12 +6729,12 @@
       <c r="F52" s="17"/>
       <c r="G52" s="17"/>
       <c r="H52" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="53" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B53" s="35" t="s">
         <v>26</v>
@@ -6747,13 +6753,13 @@
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="57"/>
       <c r="B54" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="C54" s="34" t="s">
-        <v>80</v>
-      </c>
       <c r="D54" s="34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -6762,7 +6768,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -6771,7 +6777,7 @@
       <c r="F55" s="14"/>
       <c r="G55" s="14"/>
       <c r="H55" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6783,12 +6789,12 @@
       <c r="F56" s="17"/>
       <c r="G56" s="17"/>
       <c r="H56" s="41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -6814,7 +6820,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -6835,7 +6841,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -6847,7 +6853,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -6859,7 +6865,7 @@
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -6883,7 +6889,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -6895,7 +6901,7 @@
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6907,12 +6913,12 @@
       <c r="F66" s="17"/>
       <c r="G66" s="17"/>
       <c r="H66" s="41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B67" s="50"/>
       <c r="C67" s="51"/>
@@ -6924,7 +6930,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>15</v>
@@ -6943,29 +6949,29 @@
         <v>12</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="54"/>
       <c r="B69" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C69" s="25" t="s">
         <v>19</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="H69" s="27" t="s">
         <v>96</v>
-      </c>
-      <c r="H69" s="27" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -6980,7 +6986,7 @@
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H70" s="27"/>
     </row>
@@ -6988,15 +6994,15 @@
       <c r="A71" s="54"/>
       <c r="B71" s="1"/>
       <c r="C71" s="34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H71" s="27"/>
     </row>
@@ -7024,7 +7030,7 @@
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H73" s="27"/>
     </row>
@@ -7036,7 +7042,7 @@
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H74" s="27"/>
     </row>
@@ -7048,13 +7054,13 @@
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H75" s="27"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B76" s="14"/>
       <c r="C76" s="22" t="s">
@@ -7084,7 +7090,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B78" s="14" t="s">
         <v>15</v>
@@ -7100,34 +7106,34 @@
         <v>15</v>
       </c>
       <c r="G78" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H78" s="15"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="54"/>
       <c r="B79" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="G79" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="H79" s="19"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="54"/>
       <c r="B80" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -7141,20 +7147,20 @@
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="55"/>
       <c r="B81" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C81" s="17"/>
       <c r="D81" s="17"/>
       <c r="E81" s="17"/>
       <c r="F81" s="17"/>
       <c r="G81" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H81" s="18"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="58" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B82" s="34" t="s">
         <v>26</v>
@@ -7171,14 +7177,14 @@
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="54"/>
       <c r="B83" s="34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H83" s="19"/>
     </row>
@@ -7190,7 +7196,7 @@
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H84" s="19"/>
     </row>
@@ -7202,7 +7208,7 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="45" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H85" s="19"/>
     </row>
@@ -7226,13 +7232,13 @@
       <c r="E87" s="17"/>
       <c r="F87" s="17"/>
       <c r="G87" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H87" s="18"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -7249,7 +7255,7 @@
       <c r="B89" s="17"/>
       <c r="C89" s="17"/>
       <c r="D89" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E89" s="17"/>
       <c r="F89" s="17"/>
@@ -7258,7 +7264,7 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -7302,13 +7308,13 @@
       <c r="E93" s="17"/>
       <c r="F93" s="17"/>
       <c r="G93" s="23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H93" s="18"/>
     </row>
     <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B94" s="50"/>
       <c r="C94" s="51"/>
@@ -7320,7 +7326,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="53" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B95" s="14"/>
       <c r="C95" s="14" t="s">
@@ -7340,21 +7346,21 @@
       <c r="A96" s="55"/>
       <c r="B96" s="17"/>
       <c r="C96" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D96" s="17" t="s">
         <v>16</v>
       </c>
       <c r="E96" s="17"/>
       <c r="F96" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G96" s="17"/>
       <c r="H96" s="18"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
@@ -7371,7 +7377,7 @@
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
       <c r="D98" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E98" s="17"/>
       <c r="F98" s="17"/>
@@ -7421,7 +7427,7 @@
     <mergeCell ref="A53:A54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="33" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -7438,7 +7444,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="60" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -7446,7 +7452,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="61" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="61"/>
       <c r="D5" s="61"/>
@@ -7457,16 +7463,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7539,7 +7545,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="7">
         <v>0</v>
@@ -7556,7 +7562,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="7">
         <v>0</v>
@@ -7573,7 +7579,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="7">
         <v>0</v>
@@ -7590,7 +7596,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" s="7">
         <v>0</v>
@@ -7607,7 +7613,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -7624,7 +7630,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -7641,7 +7647,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -7658,7 +7664,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -7675,7 +7681,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -7692,7 +7698,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -7709,7 +7715,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -7726,7 +7732,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -7743,7 +7749,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -7760,7 +7766,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -7777,7 +7783,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -7794,7 +7800,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -7811,7 +7817,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -7828,7 +7834,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -7845,7 +7851,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -7862,7 +7868,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -7879,7 +7885,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -7896,7 +7902,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -7913,7 +7919,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -7963,40 +7969,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S16.xlsx
+++ b/Plannings 2026 S16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5562AB7D-C39E-413F-90FA-D51330391F8C}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{85468703-40F4-4AB4-B59D-9AA85ACBEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA772512-C6E6-4EA7-805C-053DD6FB38C2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,13 +474,13 @@
     <t>21:00/22:00</t>
   </si>
   <si>
-    <t>TRAINING CUP // P50M // ANIV</t>
-  </si>
-  <si>
     <t>C. PADEL     //     EDF     //     LEAGUES     //     LDC : LIVERPOOL-PSG</t>
   </si>
   <si>
     <t>C. PADEL     //     EDF     //     LEAGUES      //      LDC : BAYERN-REAL // TOURNOI IGENSIA</t>
+  </si>
+  <si>
+    <t>TRAINING CUP FRANCE // P50M // ANIV</t>
   </si>
 </sst>
 </file>
@@ -5950,10 +5950,10 @@
         <v>137</v>
       </c>
       <c r="C3" s="63" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="63" t="s">
         <v>151</v>
-      </c>
-      <c r="D3" s="63" t="s">
-        <v>152</v>
       </c>
       <c r="E3" s="63" t="s">
         <v>138</v>
@@ -5965,7 +5965,7 @@
         <v>139</v>
       </c>
       <c r="H3" s="63" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/Plannings 2026 S16.xlsx
+++ b/Plannings 2026 S16.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
@@ -17,394 +17,464 @@
     <sheet name="Résultats par salarié" sheetId="2" r:id="rId2"/>
     <sheet name="Informations" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="153">
   <si>
+    <t>Avril-2026</t>
+  </si>
+  <si>
+    <t>Sem 16</t>
+  </si>
+  <si>
+    <t>C. PADEL // P50 // EDF // LEAGUES</t>
+  </si>
+  <si>
+    <t>C. PADEL     //     EDF     //     LEAGUES     //     LDC : LIVERPOOL-PSG</t>
+  </si>
+  <si>
+    <t>C. PADEL     //     EDF     //     LEAGUES      //      LDC : BAYERN-REAL // TOURNOI IGENSIA</t>
+  </si>
+  <si>
+    <t>C. PADEL // INAUGURATION PADEL</t>
+  </si>
+  <si>
+    <t>C. PADEL // EDF // CUP PADEL</t>
+  </si>
+  <si>
+    <t>EDF // ANIV</t>
+  </si>
+  <si>
+    <t>TRAINING CUP FRANCE // P50M // ANIV</t>
+  </si>
+  <si>
+    <t>Nom / Prénom</t>
+  </si>
+  <si>
+    <t>13 Lu</t>
+  </si>
+  <si>
+    <t>14 Ma</t>
+  </si>
+  <si>
+    <t>15 Me</t>
+  </si>
+  <si>
+    <t>16 Je</t>
+  </si>
+  <si>
+    <t>17 Ve</t>
+  </si>
+  <si>
+    <t>18 Sa</t>
+  </si>
+  <si>
+    <t>19 Di</t>
+  </si>
+  <si>
+    <t>BONILLO Matthieu</t>
+  </si>
+  <si>
+    <t>EDF-C</t>
+  </si>
+  <si>
+    <t>09:00/13:00</t>
+  </si>
+  <si>
+    <t>BOULARDET Lucas</t>
+  </si>
+  <si>
+    <t>VDC</t>
+  </si>
+  <si>
+    <t>20:00/24:00</t>
+  </si>
+  <si>
+    <t>CARRERE Peïo</t>
+  </si>
+  <si>
+    <t>15:30/19:30</t>
+  </si>
+  <si>
+    <t>16:00/18:15</t>
+  </si>
+  <si>
+    <t>17:15/19:15</t>
+  </si>
+  <si>
+    <t>16:00/17:00</t>
+  </si>
+  <si>
+    <t>L-REG</t>
+  </si>
+  <si>
+    <t>EV-RE</t>
+  </si>
+  <si>
+    <t>19:30/21:00</t>
+  </si>
+  <si>
+    <t>18:15/20:45</t>
+  </si>
+  <si>
+    <t>19:15/21:45</t>
+  </si>
+  <si>
+    <t>17:00/24:00</t>
+  </si>
+  <si>
+    <t>L-ARB</t>
+  </si>
+  <si>
+    <t>CUP-R</t>
+  </si>
+  <si>
+    <t>21:00/22:00</t>
+  </si>
+  <si>
+    <t>21:30/22:30</t>
+  </si>
+  <si>
+    <t>21:45/01:00+</t>
+  </si>
+  <si>
+    <t>20:45/24:00</t>
+  </si>
+  <si>
+    <t>CASTELLON Pascaline</t>
+  </si>
+  <si>
+    <t>07:30/13:00</t>
+  </si>
+  <si>
+    <t>COHAT Linda</t>
+  </si>
+  <si>
+    <t>CONRAD - stage David</t>
+  </si>
+  <si>
+    <t>11:45/22:00</t>
+  </si>
+  <si>
+    <t>11:35/17:00</t>
+  </si>
+  <si>
+    <t>11:30/17:00</t>
+  </si>
+  <si>
+    <t>11:30/20:00</t>
+  </si>
+  <si>
+    <t>11:30/17:30</t>
+  </si>
+  <si>
+    <t>CRUZEL Quentin</t>
+  </si>
+  <si>
+    <t>ANNIV</t>
+  </si>
+  <si>
+    <t>17:30/24:00</t>
+  </si>
+  <si>
+    <t>19:15/24:00</t>
+  </si>
+  <si>
+    <t>17:30/00:30+</t>
+  </si>
+  <si>
+    <t>13:15/17:15</t>
+  </si>
+  <si>
+    <t>17:15/22:45</t>
+  </si>
+  <si>
+    <t>DE NOUEL Maxime</t>
+  </si>
+  <si>
+    <t>C-PAD</t>
+  </si>
+  <si>
+    <t>10:45/12:15</t>
+  </si>
+  <si>
+    <t>09:45/12:15</t>
+  </si>
+  <si>
+    <t>11:45/13:15</t>
+  </si>
+  <si>
+    <t>07:30/08:45</t>
+  </si>
+  <si>
+    <t>CUP-L</t>
+  </si>
+  <si>
+    <t>PAD-A</t>
+  </si>
+  <si>
+    <t>12:30/13:00</t>
+  </si>
+  <si>
+    <t>13:30/14:15</t>
+  </si>
+  <si>
+    <t>14:15/15:45</t>
+  </si>
+  <si>
+    <t>08:45/17:15</t>
+  </si>
+  <si>
+    <t>13:00/18:00</t>
+  </si>
+  <si>
+    <t>14:15/16:45</t>
+  </si>
+  <si>
+    <t>15:45/17:30</t>
+  </si>
+  <si>
+    <t>18:00/21:15</t>
+  </si>
+  <si>
+    <t>16:45/17:45</t>
+  </si>
+  <si>
+    <t>17:30/18:30</t>
+  </si>
+  <si>
+    <t>18:15/19:15</t>
+  </si>
+  <si>
+    <t>18:30/20:30</t>
+  </si>
+  <si>
+    <t>19:15/21:15</t>
+  </si>
+  <si>
+    <t>DIVIEN Yohan</t>
+  </si>
+  <si>
+    <t>DONAER Nicolas</t>
+  </si>
+  <si>
+    <t>STAGE</t>
+  </si>
+  <si>
+    <t>09:45/14:15</t>
+  </si>
+  <si>
+    <t>18:00/00:30+</t>
+  </si>
+  <si>
+    <t>11:15/13:30</t>
+  </si>
+  <si>
+    <t>EV-LO</t>
+  </si>
+  <si>
+    <t>EDF-B</t>
+  </si>
+  <si>
+    <t>AIDE</t>
+  </si>
+  <si>
+    <t>19:15/23:30</t>
+  </si>
+  <si>
+    <t>19:15/00:15+</t>
+  </si>
+  <si>
+    <t>15:00/17:00</t>
+  </si>
+  <si>
+    <t>15:45/17:15</t>
+  </si>
+  <si>
+    <t>17:00/22:20</t>
+  </si>
+  <si>
+    <t>17:15/18:45</t>
+  </si>
+  <si>
+    <t>DOVINA Théo</t>
+  </si>
+  <si>
+    <t>20:00/00:30+</t>
+  </si>
+  <si>
+    <t>HEBERT Jean Baptiste</t>
+  </si>
+  <si>
+    <t>JARGUEL Thomas</t>
+  </si>
+  <si>
+    <t>16:00/23:40</t>
+  </si>
+  <si>
+    <t>LOUIBA Yacine</t>
+  </si>
+  <si>
+    <t>19:30/22:30</t>
+  </si>
+  <si>
+    <t>18:30/22:30</t>
+  </si>
+  <si>
+    <t>KABUNDA NDEKE Marvyn</t>
+  </si>
+  <si>
+    <t>13:45/17:45</t>
+  </si>
+  <si>
+    <t>LABEFODE Thomas</t>
+  </si>
+  <si>
+    <t>MOSTEFA Yanis</t>
+  </si>
+  <si>
+    <t>09:30/10:15</t>
+  </si>
+  <si>
+    <t>10:15/12:15</t>
+  </si>
+  <si>
+    <t>12:15/12:45</t>
+  </si>
+  <si>
+    <t>13:30/17:30</t>
+  </si>
+  <si>
+    <t>ORDONEZ GOMEZ Oceane</t>
+  </si>
+  <si>
+    <t>PEREZ Loic</t>
+  </si>
+  <si>
+    <t>17:00/22:00</t>
+  </si>
+  <si>
+    <t>09:00/09:30</t>
+  </si>
+  <si>
+    <t>11:15/13:15</t>
+  </si>
+  <si>
+    <t>17:45/21:30</t>
+  </si>
+  <si>
+    <t>09:30/12:30</t>
+  </si>
+  <si>
+    <t>13:45/15:45</t>
+  </si>
+  <si>
+    <t>15:45/17:45</t>
+  </si>
+  <si>
+    <t>PISTORE Remi</t>
+  </si>
+  <si>
+    <t>PUJOL Mathieu</t>
+  </si>
+  <si>
+    <t>EDF-A</t>
+  </si>
+  <si>
+    <t>09:45/15:30</t>
+  </si>
+  <si>
+    <t>09:45/16:00</t>
+  </si>
+  <si>
+    <t>09:45/19:00</t>
+  </si>
+  <si>
+    <t>08:45/09:45</t>
+  </si>
+  <si>
+    <t>15:30/16:00</t>
+  </si>
+  <si>
+    <t>09:45/17:30</t>
+  </si>
+  <si>
+    <t>RABII Mehdi</t>
+  </si>
+  <si>
+    <t>11:00/13:00</t>
+  </si>
+  <si>
+    <t>17:45/21:45</t>
+  </si>
+  <si>
+    <t>SANGARNE Enzo</t>
+  </si>
+  <si>
+    <t>13:45/17:30</t>
+  </si>
+  <si>
+    <t>SEIGNE Kevin</t>
+  </si>
+  <si>
+    <t>TINGUY Florian</t>
+  </si>
+  <si>
+    <t>TOPPAN Mattis</t>
+  </si>
+  <si>
+    <t>18:15/24:00</t>
+  </si>
+  <si>
+    <t>17:30/21:30</t>
+  </si>
+  <si>
+    <t>VASSANT Tiffany</t>
+  </si>
+  <si>
     <t>Planning des salariés du 13/04/2026 au 19/04/2026</t>
   </si>
   <si>
-    <t>Avril-2026</t>
-  </si>
-  <si>
-    <t>Sem 16</t>
-  </si>
-  <si>
-    <t>Nom / Prénom</t>
-  </si>
-  <si>
-    <t>13 Lu</t>
-  </si>
-  <si>
-    <t>14 Ma</t>
-  </si>
-  <si>
-    <t>15 Me</t>
-  </si>
-  <si>
-    <t>16 Je</t>
-  </si>
-  <si>
-    <t>17 Ve</t>
-  </si>
-  <si>
-    <t>18 Sa</t>
-  </si>
-  <si>
-    <t>19 Di</t>
-  </si>
-  <si>
-    <t>BONILLO Matthieu</t>
-  </si>
-  <si>
-    <t>EDF-C</t>
-  </si>
-  <si>
-    <t>09:00/13:00</t>
-  </si>
-  <si>
-    <t>BOULARDET Lucas</t>
-  </si>
-  <si>
-    <t>VDC</t>
-  </si>
-  <si>
-    <t>20:00/24:00</t>
-  </si>
-  <si>
-    <t>CARRERE Peïo</t>
-  </si>
-  <si>
-    <t>16:00/18:15</t>
-  </si>
-  <si>
-    <t>17:15/19:15</t>
-  </si>
-  <si>
-    <t>16:00/17:00</t>
-  </si>
-  <si>
-    <t>L-REG</t>
-  </si>
-  <si>
-    <t>EV-RE</t>
-  </si>
-  <si>
-    <t>18:15/20:45</t>
-  </si>
-  <si>
-    <t>19:15/21:45</t>
-  </si>
-  <si>
-    <t>17:00/24:00</t>
-  </si>
-  <si>
-    <t>L-ARB</t>
-  </si>
-  <si>
-    <t>CUP-R</t>
-  </si>
-  <si>
-    <t>20:45/24:00</t>
-  </si>
-  <si>
-    <t>21:30/22:30</t>
-  </si>
-  <si>
-    <t>21:45/01:00+</t>
-  </si>
-  <si>
-    <t>CASTELLON Pascaline</t>
-  </si>
-  <si>
-    <t>07:30/13:00</t>
-  </si>
-  <si>
-    <t>COHAT Linda</t>
-  </si>
-  <si>
-    <t>CONRAD - stage David</t>
-  </si>
-  <si>
-    <t>11:30/17:00</t>
-  </si>
-  <si>
-    <t>11:30/20:00</t>
-  </si>
-  <si>
-    <t>11:30/17:30</t>
-  </si>
-  <si>
-    <t>CRUZEL Quentin</t>
-  </si>
-  <si>
-    <t>ANNIV</t>
-  </si>
-  <si>
-    <t>19:15/24:00</t>
-  </si>
-  <si>
-    <t>17:30/00:30+</t>
-  </si>
-  <si>
-    <t>13:15/17:15</t>
-  </si>
-  <si>
-    <t>17:15/22:45</t>
-  </si>
-  <si>
-    <t>DE NOUEL Maxime</t>
-  </si>
-  <si>
-    <t>C-PAD</t>
-  </si>
-  <si>
-    <t>10:45/12:15</t>
-  </si>
-  <si>
-    <t>09:45/12:15</t>
-  </si>
-  <si>
-    <t>11:45/13:15</t>
-  </si>
-  <si>
-    <t>07:30/08:45</t>
-  </si>
-  <si>
-    <t>CUP-L</t>
-  </si>
-  <si>
-    <t>PAD-A</t>
-  </si>
-  <si>
-    <t>12:30/13:00</t>
-  </si>
-  <si>
-    <t>13:30/14:15</t>
-  </si>
-  <si>
-    <t>14:15/15:45</t>
-  </si>
-  <si>
-    <t>08:45/17:15</t>
-  </si>
-  <si>
-    <t>13:00/18:00</t>
-  </si>
-  <si>
-    <t>14:15/16:45</t>
-  </si>
-  <si>
-    <t>18:00/21:15</t>
-  </si>
-  <si>
-    <t>16:45/17:45</t>
-  </si>
-  <si>
-    <t>DIVIEN Yohan</t>
-  </si>
-  <si>
-    <t>DONAER Nicolas</t>
-  </si>
-  <si>
-    <t>STAGE</t>
-  </si>
-  <si>
-    <t>09:45/14:15</t>
-  </si>
-  <si>
-    <t>18:00/00:30+</t>
-  </si>
-  <si>
-    <t>11:15/13:30</t>
-  </si>
-  <si>
-    <t>EV-LO</t>
-  </si>
-  <si>
-    <t>EDF-B</t>
-  </si>
-  <si>
-    <t>AIDE</t>
-  </si>
-  <si>
-    <t>19:15/23:30</t>
-  </si>
-  <si>
-    <t>19:15/00:15+</t>
-  </si>
-  <si>
-    <t>15:00/17:00</t>
-  </si>
-  <si>
-    <t>15:45/17:15</t>
-  </si>
-  <si>
-    <t>17:00/22:20</t>
-  </si>
-  <si>
-    <t>17:15/18:45</t>
-  </si>
-  <si>
-    <t>DOVINA Théo</t>
-  </si>
-  <si>
-    <t>20:00/00:30+</t>
+    <t>Jour de référence : 19/04/2026</t>
+  </si>
+  <si>
+    <t>Du 13/04/2026 au 19/04/2026</t>
+  </si>
+  <si>
+    <t>COMMERCIAL DEDIES</t>
+  </si>
+  <si>
+    <t>ARBITRAGE</t>
+  </si>
+  <si>
+    <t>ANNIVERSAIRE</t>
+  </si>
+  <si>
+    <t>FORMATION</t>
   </si>
   <si>
     <t>FREIXEDAS-BERENGUER Maxime</t>
   </si>
   <si>
-    <t>19:30/22:30</t>
-  </si>
-  <si>
-    <t>18:30/22:30</t>
-  </si>
-  <si>
-    <t>HEBERT Jean Baptiste</t>
-  </si>
-  <si>
-    <t>JARGUEL Thomas</t>
-  </si>
-  <si>
-    <t>16:00/23:40</t>
-  </si>
-  <si>
-    <t>KABUNDA NDEKE Marvyn</t>
-  </si>
-  <si>
-    <t>13:45/17:45</t>
-  </si>
-  <si>
-    <t>LABEFODE Thomas</t>
-  </si>
-  <si>
-    <t>MOSTEFA Yanis</t>
-  </si>
-  <si>
-    <t>09:30/10:15</t>
-  </si>
-  <si>
-    <t>10:15/12:15</t>
-  </si>
-  <si>
-    <t>12:15/12:45</t>
-  </si>
-  <si>
-    <t>13:30/17:30</t>
-  </si>
-  <si>
-    <t>ORDONEZ GOMEZ Oceane</t>
-  </si>
-  <si>
-    <t>PEREZ Loic</t>
-  </si>
-  <si>
-    <t>17:30/24:00</t>
-  </si>
-  <si>
-    <t>17:00/22:00</t>
-  </si>
-  <si>
-    <t>09:00/09:30</t>
-  </si>
-  <si>
-    <t>11:15/13:15</t>
-  </si>
-  <si>
-    <t>17:45/21:30</t>
-  </si>
-  <si>
-    <t>09:30/12:30</t>
-  </si>
-  <si>
-    <t>13:45/15:45</t>
-  </si>
-  <si>
-    <t>15:45/17:45</t>
-  </si>
-  <si>
-    <t>PISTORE Remi</t>
-  </si>
-  <si>
-    <t>PUJOL Mathieu</t>
-  </si>
-  <si>
-    <t>EDF-A</t>
-  </si>
-  <si>
-    <t>09:45/15:30</t>
-  </si>
-  <si>
-    <t>09:45/16:00</t>
-  </si>
-  <si>
-    <t>09:45/19:00</t>
-  </si>
-  <si>
-    <t>08:45/09:45</t>
-  </si>
-  <si>
-    <t>15:30/16:00</t>
-  </si>
-  <si>
-    <t>09:45/17:30</t>
-  </si>
-  <si>
-    <t>RABII Mehdi</t>
-  </si>
-  <si>
-    <t>11:00/13:00</t>
-  </si>
-  <si>
-    <t>17:45/21:45</t>
-  </si>
-  <si>
-    <t>SANGARNE Enzo</t>
-  </si>
-  <si>
-    <t>13:45/17:30</t>
-  </si>
-  <si>
-    <t>SEIGNE Kevin</t>
-  </si>
-  <si>
-    <t>TINGUY Florian</t>
-  </si>
-  <si>
-    <t>TOPPAN Mattis</t>
-  </si>
-  <si>
-    <t>18:15/24:00</t>
-  </si>
-  <si>
-    <t>17:30/21:30</t>
-  </si>
-  <si>
-    <t>VASSANT Tiffany</t>
-  </si>
-  <si>
-    <t>Jour de référence : 19/04/2026</t>
-  </si>
-  <si>
-    <t>Du 13/04/2026 au 19/04/2026</t>
-  </si>
-  <si>
-    <t>COMMERCIAL DEDIES</t>
-  </si>
-  <si>
-    <t>ARBITRAGE</t>
-  </si>
-  <si>
-    <t>ANNIVERSAIRE</t>
-  </si>
-  <si>
-    <t>FORMATION</t>
-  </si>
-  <si>
     <t>Société</t>
   </si>
   <si>
@@ -427,60 +497,6 @@
   </si>
   <si>
     <t>02/04/2026 21:49</t>
-  </si>
-  <si>
-    <t>LOUIBA Yacine</t>
-  </si>
-  <si>
-    <t>C. PADEL // EDF // CUP PADEL</t>
-  </si>
-  <si>
-    <t>C. PADEL // P50 // EDF // LEAGUES</t>
-  </si>
-  <si>
-    <t>C. PADEL // INAUGURATION PADEL</t>
-  </si>
-  <si>
-    <t>EDF // ANIV</t>
-  </si>
-  <si>
-    <t>15:45/17:30</t>
-  </si>
-  <si>
-    <t>18:30/20:30</t>
-  </si>
-  <si>
-    <t>17:30/18:30</t>
-  </si>
-  <si>
-    <t>18:15/19:15</t>
-  </si>
-  <si>
-    <t>19:15/21:15</t>
-  </si>
-  <si>
-    <t>11:45/22:00</t>
-  </si>
-  <si>
-    <t>11:35/17:00</t>
-  </si>
-  <si>
-    <t>15:30/19:30</t>
-  </si>
-  <si>
-    <t>19:30/21:00</t>
-  </si>
-  <si>
-    <t>21:00/22:00</t>
-  </si>
-  <si>
-    <t>C. PADEL     //     EDF     //     LEAGUES     //     LDC : LIVERPOOL-PSG</t>
-  </si>
-  <si>
-    <t>C. PADEL     //     EDF     //     LEAGUES      //      LDC : BAYERN-REAL // TOURNOI IGENSIA</t>
-  </si>
-  <si>
-    <t>TRAINING CUP FRANCE // P50M // ANIV</t>
   </si>
 </sst>
 </file>
@@ -490,7 +506,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -527,51 +543,12 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
     </font>
     <font>
       <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
@@ -882,7 +859,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -893,29 +870,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -980,16 +936,16 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1001,25 +957,25 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1031,6 +987,39 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1040,41 +1029,26 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5918,1493 +5892,1483 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="59" t="s">
+    <row r="1" spans="1:8">
+      <c r="B1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="B2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+    </row>
+    <row r="3" spans="1:8" s="44" customFormat="1" ht="25.5">
+      <c r="B3" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-    </row>
-    <row r="3" spans="1:8" s="62" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="63" t="s">
-        <v>137</v>
-      </c>
-      <c r="C3" s="63" t="s">
-        <v>150</v>
-      </c>
-      <c r="D3" s="63" t="s">
-        <v>151</v>
-      </c>
-      <c r="E3" s="63" t="s">
-        <v>138</v>
-      </c>
-      <c r="F3" s="63" t="s">
-        <v>136</v>
-      </c>
-      <c r="G3" s="63" t="s">
-        <v>139</v>
-      </c>
-      <c r="H3" s="63" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="C3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="D3" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="E3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="F3" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="G3" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="H3" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="12" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="22" t="s">
+      <c r="D4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="15"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="55"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="23" t="s">
+      <c r="E4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="18"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
+      <c r="F4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14" t="s">
+      <c r="G4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="55"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17" t="s">
+      <c r="H4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="53" t="s">
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="15"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A6" s="49"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A8" s="49"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="50"/>
       <c r="B10" s="1" t="s">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="19"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="54"/>
-      <c r="B11" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>22</v>
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="50"/>
+      <c r="B11" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>29</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="19"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="54"/>
-      <c r="B12" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="29" t="s">
-        <v>25</v>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="50"/>
+      <c r="B12" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="19"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="54"/>
-      <c r="B13" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="29"/>
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="50"/>
+      <c r="B13" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="22"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="19"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="57"/>
-      <c r="B14" s="34" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="29"/>
+      <c r="H13" s="12"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="51"/>
+      <c r="B14" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="22"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="19"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="57"/>
+      <c r="H14" s="12"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="51"/>
       <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
+        <v>21</v>
+      </c>
+      <c r="C15" s="27"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="19"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="55"/>
-      <c r="B16" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="53" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="32" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="55"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="49" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="52"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="14"/>
-      <c r="H20" s="15"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="55"/>
-      <c r="B21" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="D21" s="17" t="s">
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A16" s="49"/>
+      <c r="B16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="29"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="G21" s="17"/>
-      <c r="H21" s="18"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="H22" s="15"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="54"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A18" s="49"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A19" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="54"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="56"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A21" s="49"/>
+      <c r="B21" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="50"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="64" t="s">
-        <v>93</v>
+      <c r="C23" s="46" t="s">
+        <v>51</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G23" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" s="19"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="54"/>
+        <v>53</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" s="12"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="50"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="57"/>
+        <v>21</v>
+      </c>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A25" s="51"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H25" s="19"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="47" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="54"/>
-      <c r="B27" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="H25" s="12"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="50"/>
+      <c r="B27" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="48" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="54"/>
+      <c r="H27" s="41" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="50"/>
       <c r="B28" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" s="29"/>
+        <v>63</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="22"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="54"/>
+      <c r="H28" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="50"/>
       <c r="B29" s="1" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="29"/>
+        <v>65</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="22"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="54"/>
-      <c r="B30" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="37" t="s">
-        <v>45</v>
+      <c r="H29" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="50"/>
+      <c r="B30" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>57</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" s="29"/>
+        <v>63</v>
+      </c>
+      <c r="E30" s="22"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="19"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="54"/>
-      <c r="B31" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>57</v>
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="50"/>
+      <c r="B31" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>69</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E31" s="29"/>
+        <v>70</v>
+      </c>
+      <c r="E31" s="22"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="19"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="54"/>
-      <c r="B32" s="26" t="s">
-        <v>45</v>
+      <c r="H31" s="12"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="50"/>
+      <c r="B32" s="19" t="s">
+        <v>57</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="E32" s="29"/>
+        <v>63</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="22"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="19"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="54"/>
-      <c r="B33" s="25" t="s">
-        <v>58</v>
+      <c r="H32" s="12"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="50"/>
+      <c r="B33" s="18" t="s">
+        <v>71</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>142</v>
-      </c>
-      <c r="E33" s="29"/>
+        <v>72</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="22"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="19"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="54"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" s="29"/>
+      <c r="H33" s="12"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="50"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E34" s="22"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="19"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="57"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="E35" s="29"/>
+      <c r="H34" s="12"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="51"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" s="22"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="19"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="57"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D36" s="25"/>
-      <c r="E36" s="29"/>
+      <c r="H35" s="12"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="51"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="18"/>
+      <c r="E36" s="22"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="19"/>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="55"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="D37" s="23"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="18"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H38" s="15"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="55"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" s="18"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" s="14"/>
-      <c r="H40" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="54"/>
-      <c r="B41" s="25" t="s">
+      <c r="H36" s="12"/>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A37" s="49"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="16"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="11"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A39" s="49"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="16" t="s">
         <v>19</v>
+      </c>
+      <c r="H39" s="11"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" s="7"/>
+      <c r="H40" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="50"/>
+      <c r="B41" s="18" t="s">
+        <v>26</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F41" s="25" t="s">
-        <v>19</v>
+        <v>81</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>26</v>
       </c>
       <c r="G41" s="1"/>
-      <c r="H41" s="27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="54"/>
-      <c r="B42" s="31" t="s">
-        <v>66</v>
+      <c r="H41" s="20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="50"/>
+      <c r="B42" s="24" t="s">
+        <v>83</v>
       </c>
       <c r="C42" s="1"/>
-      <c r="D42" s="26" t="s">
-        <v>67</v>
+      <c r="D42" s="19" t="s">
+        <v>84</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G42" s="1"/>
-      <c r="H42" s="42" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="54"/>
-      <c r="B43" s="29" t="s">
-        <v>69</v>
+      <c r="H42" s="35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="50"/>
+      <c r="B43" s="22" t="s">
+        <v>86</v>
       </c>
       <c r="C43" s="1"/>
-      <c r="D43" s="25" t="s">
-        <v>54</v>
+      <c r="D43" s="18" t="s">
+        <v>66</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="G43" s="1"/>
-      <c r="H43" s="43" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="54"/>
-      <c r="B44" s="29"/>
+      <c r="H43" s="36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="50"/>
+      <c r="B44" s="22"/>
       <c r="C44" s="1"/>
       <c r="D44" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
-      <c r="H44" s="21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="54"/>
-      <c r="B45" s="29"/>
+      <c r="H44" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="50"/>
+      <c r="B45" s="22"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
-      <c r="H45" s="19" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="54"/>
-      <c r="B46" s="29"/>
+      <c r="H45" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="50"/>
+      <c r="B46" s="22"/>
       <c r="C46" s="1"/>
-      <c r="D46" s="26" t="s">
-        <v>67</v>
+      <c r="D46" s="19" t="s">
+        <v>84</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
-      <c r="H46" s="19"/>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="55"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="18"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="15"/>
-    </row>
-    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="55"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="18"/>
-    </row>
-    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B50" s="50"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="52"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="55"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="B53" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="C53" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="D53" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="15"/>
-    </row>
-    <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="57"/>
-      <c r="B54" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C54" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="D54" s="34" t="s">
-        <v>78</v>
+      <c r="H46" s="12"/>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A47" s="49"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="11"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="8"/>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A49" s="49"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="11"/>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A50" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" s="54"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="55"/>
+      <c r="E50" s="55"/>
+      <c r="F50" s="55"/>
+      <c r="G50" s="55"/>
+      <c r="H50" s="56"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A52" s="49"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="8"/>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A54" s="51"/>
+      <c r="B54" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D54" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="19"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="53" t="s">
-        <v>83</v>
-      </c>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="55"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="41" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G57" s="14"/>
-      <c r="H57" s="15"/>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="55"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G58" s="17"/>
-      <c r="H58" s="18"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="54"/>
+      <c r="H54" s="12"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A56" s="49"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="34" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" s="7"/>
+      <c r="H57" s="8"/>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A58" s="49"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="10"/>
+      <c r="H58" s="11"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="50"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="54"/>
+      <c r="H60" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="50"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="42" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="54"/>
+      <c r="H61" s="35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="50"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
-      <c r="H62" s="43" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="54"/>
+      <c r="H62" s="36" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="50"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
-      <c r="H63" s="21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="54"/>
+      <c r="H63" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="50"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
-      <c r="H64" s="19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="54"/>
+      <c r="H64" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="50"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
-      <c r="H65" s="42" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="55"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="41" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="B67" s="50"/>
-      <c r="C67" s="51"/>
-      <c r="D67" s="51"/>
-      <c r="E67" s="51"/>
-      <c r="F67" s="51"/>
-      <c r="G67" s="51"/>
-      <c r="H67" s="52"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C68" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D68" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E68" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F68" s="14"/>
-      <c r="G68" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H68" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="54"/>
+      <c r="H65" s="35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A66" s="49"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="10"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A67" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B67" s="54"/>
+      <c r="C67" s="55"/>
+      <c r="D67" s="55"/>
+      <c r="E67" s="55"/>
+      <c r="F67" s="55"/>
+      <c r="G67" s="55"/>
+      <c r="H67" s="56"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F68" s="7"/>
+      <c r="G68" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="50"/>
       <c r="B69" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C69" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D69" s="25" t="s">
-        <v>84</v>
+        <v>51</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>101</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="F69" s="1"/>
-      <c r="G69" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="H69" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="54"/>
+      <c r="G69" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="H69" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="50"/>
       <c r="B70" s="1"/>
-      <c r="C70" s="33" t="s">
-        <v>26</v>
+      <c r="C70" s="26" t="s">
+        <v>34</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="H70" s="27"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="54"/>
+      <c r="G70" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H70" s="20"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="50"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="34" t="s">
-        <v>78</v>
+      <c r="C71" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="H71" s="27"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="54"/>
+      <c r="G71" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="H71" s="20"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="50"/>
       <c r="B72" s="1"/>
-      <c r="C72" s="34"/>
-      <c r="D72" s="33" t="s">
-        <v>26</v>
+      <c r="C72" s="27"/>
+      <c r="D72" s="26" t="s">
+        <v>34</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-      <c r="G72" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="H72" s="27"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="54"/>
+      <c r="G72" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H72" s="20"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="50"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="34"/>
-      <c r="D73" s="34" t="s">
-        <v>29</v>
+      <c r="C73" s="27"/>
+      <c r="D73" s="27" t="s">
+        <v>37</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
-      <c r="G73" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="H73" s="27"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="54"/>
+      <c r="G73" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="H73" s="20"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="50"/>
       <c r="B74" s="1"/>
-      <c r="C74" s="34"/>
-      <c r="D74" s="34"/>
+      <c r="C74" s="27"/>
+      <c r="D74" s="27"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
-      <c r="G74" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="H74" s="27"/>
-    </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="57"/>
+      <c r="G74" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="H74" s="20"/>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A75" s="51"/>
       <c r="B75" s="1"/>
-      <c r="C75" s="34"/>
-      <c r="D75" s="34"/>
+      <c r="C75" s="27"/>
+      <c r="D75" s="27"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="45" t="s">
-        <v>100</v>
-      </c>
-      <c r="H75" s="27"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="B76" s="14"/>
-      <c r="C76" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G76" s="14"/>
-      <c r="H76" s="15"/>
-    </row>
-    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="55"/>
-      <c r="B77" s="17"/>
-      <c r="C77" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G77" s="17"/>
-      <c r="H77" s="18"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C78" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F78" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G78" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="H78" s="15"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="54"/>
+      <c r="G75" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="H75" s="20"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="B76" s="7"/>
+      <c r="C76" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" s="7"/>
+      <c r="H76" s="8"/>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A77" s="49"/>
+      <c r="B77" s="10"/>
+      <c r="C77" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D77" s="10"/>
+      <c r="E77" s="10"/>
+      <c r="F77" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="10"/>
+      <c r="H77" s="11"/>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H78" s="8"/>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="50"/>
       <c r="B79" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="H79" s="19"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="54"/>
-      <c r="B80" s="31" t="s">
-        <v>66</v>
+        <v>123</v>
+      </c>
+      <c r="H79" s="12"/>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="50"/>
+      <c r="B80" s="24" t="s">
+        <v>83</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H80" s="19"/>
-    </row>
-    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="55"/>
-      <c r="B81" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
-      <c r="G81" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="H81" s="18"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="58" t="s">
-        <v>110</v>
-      </c>
-      <c r="B82" s="34" t="s">
-        <v>26</v>
+        <v>21</v>
+      </c>
+      <c r="H80" s="12"/>
+    </row>
+    <row r="81" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A81" s="49"/>
+      <c r="B81" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C81" s="10"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10"/>
+      <c r="G81" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H81" s="11"/>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="B82" s="27" t="s">
+        <v>34</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H82" s="19"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="54"/>
-      <c r="B83" s="34" t="s">
-        <v>78</v>
+        <v>21</v>
+      </c>
+      <c r="H82" s="12"/>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="50"/>
+      <c r="B83" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H83" s="19"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="54"/>
-      <c r="B84" s="34"/>
+        <v>127</v>
+      </c>
+      <c r="H83" s="12"/>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="50"/>
+      <c r="B84" s="27"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
-      <c r="G84" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="H84" s="19"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="54"/>
-      <c r="B85" s="34"/>
+      <c r="G84" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="H84" s="12"/>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="50"/>
+      <c r="B85" s="27"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
-      <c r="G85" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="H85" s="19"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="54"/>
-      <c r="B86" s="34"/>
+      <c r="G85" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="H85" s="12"/>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="50"/>
+      <c r="B86" s="27"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
       <c r="G86" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H86" s="19"/>
-    </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="55"/>
-      <c r="B87" s="36"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="17"/>
-      <c r="F87" s="17"/>
-      <c r="G87" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H87" s="18"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="B88" s="14"/>
-      <c r="C88" s="14"/>
-      <c r="D88" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="H88" s="15"/>
-    </row>
-    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="55"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
-      <c r="D89" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E89" s="17"/>
-      <c r="F89" s="17"/>
-      <c r="G89" s="17"/>
-      <c r="H89" s="18"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="B90" s="14"/>
-      <c r="C90" s="14"/>
-      <c r="D90" s="14"/>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H90" s="15"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="54"/>
+        <v>21</v>
+      </c>
+      <c r="H86" s="12"/>
+    </row>
+    <row r="87" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A87" s="49"/>
+      <c r="B87" s="29"/>
+      <c r="C87" s="10"/>
+      <c r="D87" s="10"/>
+      <c r="E87" s="10"/>
+      <c r="F87" s="10"/>
+      <c r="G87" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H87" s="11"/>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="B88" s="7"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="7"/>
+      <c r="H88" s="8"/>
+    </row>
+    <row r="89" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A89" s="49"/>
+      <c r="B89" s="10"/>
+      <c r="C89" s="10"/>
+      <c r="D89" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E89" s="10"/>
+      <c r="F89" s="10"/>
+      <c r="G89" s="10"/>
+      <c r="H89" s="11"/>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="B90" s="7"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="7"/>
+      <c r="G90" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H90" s="8"/>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="50"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
-      <c r="G91" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="H91" s="19"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="54"/>
+      <c r="G91" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" s="12"/>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="50"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
-      <c r="G92" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="H92" s="19"/>
-    </row>
-    <row r="93" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="55"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="17"/>
-      <c r="D93" s="17"/>
-      <c r="E93" s="17"/>
-      <c r="F93" s="17"/>
-      <c r="G93" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="H93" s="18"/>
-    </row>
-    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B94" s="50"/>
-      <c r="C94" s="51"/>
-      <c r="D94" s="51"/>
-      <c r="E94" s="51"/>
-      <c r="F94" s="51"/>
-      <c r="G94" s="51"/>
-      <c r="H94" s="52"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="B95" s="14"/>
-      <c r="C95" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E95" s="14"/>
-      <c r="F95" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="G95" s="14"/>
-      <c r="H95" s="15"/>
-    </row>
-    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="55"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="D96" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E96" s="17"/>
-      <c r="F96" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="G96" s="17"/>
-      <c r="H96" s="18"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="B97" s="14"/>
-      <c r="C97" s="14"/>
-      <c r="D97" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E97" s="14"/>
-      <c r="F97" s="14"/>
-      <c r="G97" s="14"/>
-      <c r="H97" s="15"/>
-    </row>
-    <row r="98" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="55"/>
-      <c r="B98" s="17"/>
-      <c r="C98" s="17"/>
-      <c r="D98" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E98" s="17"/>
-      <c r="F98" s="17"/>
-      <c r="G98" s="17"/>
-      <c r="H98" s="18"/>
-    </row>
-    <row r="99" spans="1:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="56"/>
-      <c r="C99" s="56"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="56"/>
-      <c r="F99" s="56"/>
-      <c r="G99" s="56"/>
-      <c r="H99" s="56"/>
+      <c r="G92" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H92" s="12"/>
+    </row>
+    <row r="93" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A93" s="49"/>
+      <c r="B93" s="10"/>
+      <c r="C93" s="10"/>
+      <c r="D93" s="10"/>
+      <c r="E93" s="10"/>
+      <c r="F93" s="10"/>
+      <c r="G93" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="H93" s="11"/>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A94" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B94" s="54"/>
+      <c r="C94" s="55"/>
+      <c r="D94" s="55"/>
+      <c r="E94" s="55"/>
+      <c r="F94" s="55"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="56"/>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="B95" s="7"/>
+      <c r="C95" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E95" s="7"/>
+      <c r="F95" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G95" s="7"/>
+      <c r="H95" s="8"/>
+    </row>
+    <row r="96" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A96" s="49"/>
+      <c r="B96" s="10"/>
+      <c r="C96" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E96" s="10"/>
+      <c r="F96" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="G96" s="10"/>
+      <c r="H96" s="11"/>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="8"/>
+    </row>
+    <row r="98" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A98" s="49"/>
+      <c r="B98" s="10"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E98" s="10"/>
+      <c r="F98" s="10"/>
+      <c r="G98" s="10"/>
+      <c r="H98" s="11"/>
+    </row>
+    <row r="99" spans="1:8" ht="4.5" customHeight="1">
+      <c r="B99" s="52"/>
+      <c r="C99" s="52"/>
+      <c r="D99" s="52"/>
+      <c r="E99" s="52"/>
+      <c r="F99" s="52"/>
+      <c r="G99" s="52"/>
+      <c r="H99" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A37"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="A95:A96"/>
     <mergeCell ref="A97:A98"/>
     <mergeCell ref="B99:H99"/>
     <mergeCell ref="A68:A75"/>
@@ -7412,11 +7376,16 @@
     <mergeCell ref="A78:A81"/>
     <mergeCell ref="A82:A87"/>
     <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B94:H94"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A37"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="A95:A96"/>
     <mergeCell ref="B50:H50"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B67:H67"/>
-    <mergeCell ref="B94:H94"/>
-    <mergeCell ref="A90:A93"/>
     <mergeCell ref="A51:A52"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="A57:A58"/>
@@ -7425,6 +7394,11 @@
     <mergeCell ref="A40:A47"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A16"/>
+    <mergeCell ref="A17:A18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -7435,516 +7409,516 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="60" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="61" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="60">
+        <v>0</v>
+      </c>
+      <c r="C7" s="60">
+        <v>0</v>
+      </c>
+      <c r="D7" s="60">
+        <v>0</v>
+      </c>
+      <c r="E7" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="59" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="60">
+        <v>0</v>
+      </c>
+      <c r="C8" s="60">
+        <v>0</v>
+      </c>
+      <c r="D8" s="60">
+        <v>0</v>
+      </c>
+      <c r="E8" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="60">
+        <v>0</v>
+      </c>
+      <c r="C9" s="60">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="D9" s="60">
+        <v>0</v>
+      </c>
+      <c r="E9" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="60">
+        <v>0</v>
+      </c>
+      <c r="C10" s="60">
+        <v>0</v>
+      </c>
+      <c r="D10" s="60">
+        <v>0</v>
+      </c>
+      <c r="E10" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="60">
+        <v>0</v>
+      </c>
+      <c r="C11" s="60">
+        <v>0</v>
+      </c>
+      <c r="D11" s="60">
+        <v>0</v>
+      </c>
+      <c r="E11" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="60">
+        <v>0</v>
+      </c>
+      <c r="C12" s="60">
+        <v>0</v>
+      </c>
+      <c r="D12" s="60">
+        <v>0</v>
+      </c>
+      <c r="E12" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="60">
+        <v>0</v>
+      </c>
+      <c r="C13" s="60">
+        <v>0</v>
+      </c>
+      <c r="D13" s="60">
+        <v>0.16111200000000001</v>
+      </c>
+      <c r="E13" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="60">
+        <v>0</v>
+      </c>
+      <c r="C14" s="60">
+        <v>0</v>
+      </c>
+      <c r="D14" s="60">
+        <v>0</v>
+      </c>
+      <c r="E14" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="59" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="60">
+        <v>0</v>
+      </c>
+      <c r="C15" s="60">
+        <v>0</v>
+      </c>
+      <c r="D15" s="60">
+        <v>0</v>
+      </c>
+      <c r="E15" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="60">
+        <v>0</v>
+      </c>
+      <c r="C16" s="60">
+        <v>0</v>
+      </c>
+      <c r="D16" s="60">
+        <v>0</v>
+      </c>
+      <c r="E16" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="59" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="60">
+        <v>0</v>
+      </c>
+      <c r="C17" s="60">
+        <v>0</v>
+      </c>
+      <c r="D17" s="60">
+        <v>0</v>
+      </c>
+      <c r="E17" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="59" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="60">
+        <v>0</v>
+      </c>
+      <c r="C18" s="60">
+        <v>0.41666700000000001</v>
+      </c>
+      <c r="D18" s="60">
+        <v>0</v>
+      </c>
+      <c r="E18" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="60">
+        <v>0</v>
+      </c>
+      <c r="C19" s="60">
+        <v>0</v>
+      </c>
+      <c r="D19" s="60">
+        <v>0</v>
+      </c>
+      <c r="E19" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" s="60">
+        <v>0</v>
+      </c>
+      <c r="C20" s="60">
+        <v>0</v>
+      </c>
+      <c r="D20" s="60">
+        <v>0</v>
+      </c>
+      <c r="E20" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="59" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="60">
+        <v>0</v>
+      </c>
+      <c r="C21" s="60">
+        <v>0</v>
+      </c>
+      <c r="D21" s="60">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="E21" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="59" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="60">
+        <v>0</v>
+      </c>
+      <c r="C22" s="60">
+        <v>0</v>
+      </c>
+      <c r="D22" s="60">
+        <v>0</v>
+      </c>
+      <c r="E22" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="60">
+        <v>0</v>
+      </c>
+      <c r="C23" s="60">
+        <v>0</v>
+      </c>
+      <c r="D23" s="60">
+        <v>0.25</v>
+      </c>
+      <c r="E23" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="60">
+        <v>0</v>
+      </c>
+      <c r="C24" s="60">
+        <v>0</v>
+      </c>
+      <c r="D24" s="60">
+        <v>0</v>
+      </c>
+      <c r="E24" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" s="60">
+        <v>0</v>
+      </c>
+      <c r="C25" s="60">
+        <v>0.16527800000000001</v>
+      </c>
+      <c r="D25" s="60">
+        <v>8.3334000000000005E-2</v>
+      </c>
+      <c r="E25" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="60">
+        <v>0</v>
+      </c>
+      <c r="C26" s="60">
+        <v>0</v>
+      </c>
+      <c r="D26" s="60">
+        <v>0</v>
+      </c>
+      <c r="E26" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="60">
+        <v>0</v>
+      </c>
+      <c r="C27" s="60">
+        <v>0</v>
+      </c>
+      <c r="D27" s="60">
+        <v>0</v>
+      </c>
+      <c r="E27" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="59" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="7">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="7">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="7">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7">
-        <v>4.1667000000000003E-2</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="7">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="7">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="7">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="7">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7">
-        <v>0.16111200000000001</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="7">
-        <v>0</v>
-      </c>
-      <c r="C14" s="7">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0</v>
-      </c>
-      <c r="C15" s="7">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7">
-        <v>0</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="7">
-        <v>0</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7">
-        <v>0</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="7">
-        <v>0</v>
-      </c>
-      <c r="C17" s="7">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="7">
-        <v>0</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.41666700000000001</v>
-      </c>
-      <c r="D18" s="7">
-        <v>0</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B19" s="7">
-        <v>0</v>
-      </c>
-      <c r="C19" s="7">
-        <v>0</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B20" s="7">
-        <v>0</v>
-      </c>
-      <c r="C20" s="7">
-        <v>0</v>
-      </c>
-      <c r="D20" s="7">
-        <v>0</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="7">
-        <v>0</v>
-      </c>
-      <c r="C21" s="7">
-        <v>0</v>
-      </c>
-      <c r="D21" s="7">
-        <v>0.16666700000000001</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="7">
-        <v>0</v>
-      </c>
-      <c r="C22" s="7">
-        <v>0</v>
-      </c>
-      <c r="D22" s="7">
-        <v>0</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" s="7">
-        <v>0</v>
-      </c>
-      <c r="C23" s="7">
-        <v>0</v>
-      </c>
-      <c r="D23" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="7">
-        <v>0</v>
-      </c>
-      <c r="C24" s="7">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7">
-        <v>0</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="7">
-        <v>0</v>
-      </c>
-      <c r="C25" s="7">
-        <v>0.16527800000000001</v>
-      </c>
-      <c r="D25" s="7">
-        <v>8.3334000000000005E-2</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B26" s="7">
-        <v>0</v>
-      </c>
-      <c r="C26" s="7">
-        <v>0</v>
-      </c>
-      <c r="D26" s="7">
-        <v>0</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B27" s="7">
-        <v>0</v>
-      </c>
-      <c r="C27" s="7">
-        <v>0</v>
-      </c>
-      <c r="D27" s="7">
-        <v>0</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B28" s="7">
-        <v>0</v>
-      </c>
-      <c r="C28" s="7">
+      <c r="B28" s="60">
+        <v>0</v>
+      </c>
+      <c r="C28" s="60">
         <v>0.125</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="60">
         <v>0.159723</v>
       </c>
-      <c r="E28" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B29" s="7">
-        <v>0</v>
-      </c>
-      <c r="C29" s="7">
-        <v>0</v>
-      </c>
-      <c r="D29" s="7">
-        <v>0</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" s="7">
-        <v>0</v>
-      </c>
-      <c r="C30" s="7">
-        <v>0</v>
-      </c>
-      <c r="D30" s="7">
-        <v>0</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31" s="7">
-        <v>0</v>
-      </c>
-      <c r="C31" s="7">
-        <v>0</v>
-      </c>
-      <c r="D31" s="7">
-        <v>0</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B32" s="7">
-        <v>0</v>
-      </c>
-      <c r="C32" s="7">
-        <v>0</v>
-      </c>
-      <c r="D32" s="7">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B33" s="7">
-        <v>0</v>
-      </c>
-      <c r="C33" s="7">
-        <v>0</v>
-      </c>
-      <c r="D33" s="7">
-        <v>0</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="8">
-        <v>0</v>
-      </c>
-      <c r="C34" s="8">
+      <c r="E28" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29" s="60">
+        <v>0</v>
+      </c>
+      <c r="C29" s="60">
+        <v>0</v>
+      </c>
+      <c r="D29" s="60">
+        <v>0</v>
+      </c>
+      <c r="E29" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="60">
+        <v>0</v>
+      </c>
+      <c r="C30" s="60">
+        <v>0</v>
+      </c>
+      <c r="D30" s="60">
+        <v>0</v>
+      </c>
+      <c r="E30" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="B31" s="60">
+        <v>0</v>
+      </c>
+      <c r="C31" s="60">
+        <v>0</v>
+      </c>
+      <c r="D31" s="60">
+        <v>0</v>
+      </c>
+      <c r="E31" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="59" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="60">
+        <v>0</v>
+      </c>
+      <c r="C32" s="60">
+        <v>0</v>
+      </c>
+      <c r="D32" s="60">
+        <v>0</v>
+      </c>
+      <c r="E32" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="B33" s="60">
+        <v>0</v>
+      </c>
+      <c r="C33" s="60">
+        <v>0</v>
+      </c>
+      <c r="D33" s="60">
+        <v>0</v>
+      </c>
+      <c r="E33" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="B34" s="61">
+        <v>0</v>
+      </c>
+      <c r="C34" s="61">
         <v>0.74861200000000006</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="61">
         <v>0.82083399999999995</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="61">
         <v>0</v>
       </c>
     </row>
@@ -7960,49 +7934,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B5" s="11"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>134</v>
+    <row r="1" spans="1:2" ht="15.75">
+      <c r="A1" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="63" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="63"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="62" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="62" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" s="63" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="62" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -8012,12 +7986,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3c298670-db79-47a5-968d-a4570c34317f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="17e8e7ea-beb0-4155-adc4-5bfa61f32508" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8166,50 +8142,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3c298670-db79-47a5-968d-a4570c34317f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="17e8e7ea-beb0-4155-adc4-5bfa61f32508" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A229E62-260D-48FB-941B-1FC4CE57FFA1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A2781D-D577-4B30-9A10-4D3F148A4425}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{818E86A5-F5EA-4119-9955-C95B5A21FA8C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
-    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{818E86A5-F5EA-4119-9955-C95B5A21FA8C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A2781D-D577-4B30-9A10-4D3F148A4425}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
-    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A229E62-260D-48FB-941B-1FC4CE57FFA1}"/>
 </file>